--- a/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
+++ b/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
@@ -1141,7 +1141,7 @@
     <t>-4016518746</t>
   </si>
   <si>
-    <t>-954752748</t>
+    <t>-912522379</t>
   </si>
   <si>
     <t>-4804060590</t>

--- a/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
+++ b/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="690">
   <si>
     <t>THÔNG TIN KHO</t>
   </si>
@@ -715,6 +715,9 @@
     <t>A255</t>
   </si>
   <si>
+    <t>A247</t>
+  </si>
+  <si>
     <t>-4776256360</t>
   </si>
   <si>
@@ -1390,6 +1393,15 @@
     <t>-5588180836</t>
   </si>
   <si>
+    <t>-1003906666364</t>
+  </si>
+  <si>
+    <t>-1003991560755</t>
+  </si>
+  <si>
+    <t>-1004367466882</t>
+  </si>
+  <si>
     <t>KFM_BDU_DAN - 27 Tân Lập</t>
   </si>
   <si>
@@ -2069,6 +2081,9 @@
   </si>
   <si>
     <t>KFM_HCM_Q7 - A255 (Green View)</t>
+  </si>
+  <si>
+    <t>KFM_HCM_BTA - DC - A247 (Lê Cơ)</t>
   </si>
 </sst>
 </file>
@@ -2400,7 +2415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D228"/>
+  <dimension ref="A1:D229"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2425,10 +2440,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2439,10 +2454,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D3" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2453,10 +2468,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D4" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2467,10 +2482,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D5" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2481,10 +2496,10 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D6" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2495,10 +2510,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D7" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2509,10 +2524,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D8" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2523,10 +2538,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D9" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2537,10 +2552,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D10" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2551,10 +2566,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D11" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2565,10 +2580,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D12" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2579,10 +2594,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D13" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2593,10 +2608,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D14" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2607,10 +2622,10 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D15" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2621,10 +2636,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D16" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2635,10 +2650,10 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D17" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2649,10 +2664,10 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D18" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2663,10 +2678,10 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D19" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2677,10 +2692,10 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D20" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2691,10 +2706,10 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D21" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2705,10 +2720,10 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D22" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2719,10 +2734,10 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D23" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2733,10 +2748,10 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D24" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2747,10 +2762,10 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D25" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2761,10 +2776,10 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D26" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2775,10 +2790,10 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D27" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2789,10 +2804,10 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D28" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2803,10 +2818,10 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2817,10 +2832,10 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D30" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2831,10 +2846,10 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D31" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2845,10 +2860,10 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2859,10 +2874,10 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D33" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2873,10 +2888,10 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2887,10 +2902,10 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D35" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2901,10 +2916,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D36" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2915,10 +2930,10 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D37" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2929,10 +2944,10 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D38" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2943,10 +2958,10 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D39" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2957,10 +2972,10 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D40" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2971,10 +2986,10 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D41" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2985,10 +3000,10 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D42" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2999,10 +3014,10 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D43" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3013,10 +3028,10 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D44" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3027,10 +3042,10 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D45" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3041,10 +3056,10 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D46" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3055,10 +3070,10 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D47" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3069,10 +3084,10 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D48" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3083,10 +3098,10 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D49" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3097,10 +3112,10 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D50" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3111,10 +3126,10 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D51" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3125,10 +3140,10 @@
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D52" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3139,10 +3154,10 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D53" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3153,10 +3168,10 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D54" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3167,10 +3182,10 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D55" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3181,10 +3196,10 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D56" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3195,10 +3210,10 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D57" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3209,10 +3224,10 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D58" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3223,10 +3238,10 @@
         <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D59" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3237,10 +3252,10 @@
         <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D60" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3251,10 +3266,10 @@
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D61" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3265,10 +3280,10 @@
         <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D62" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3279,10 +3294,10 @@
         <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D63" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3293,10 +3308,10 @@
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D64" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3307,10 +3322,10 @@
         <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D65" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3321,10 +3336,10 @@
         <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D66" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3335,10 +3350,10 @@
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D67" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3349,10 +3364,10 @@
         <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D68" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3363,10 +3378,10 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D69" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3377,10 +3392,10 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D70" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3391,10 +3406,10 @@
         <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D71" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3405,10 +3420,10 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D72" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3419,10 +3434,10 @@
         <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D73" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3433,10 +3448,10 @@
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D74" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3447,10 +3462,10 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D75" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3461,10 +3476,10 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D76" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3475,10 +3490,10 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D77" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3489,10 +3504,10 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D78" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3503,10 +3518,10 @@
         <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D79" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3517,10 +3532,10 @@
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D80" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3531,10 +3546,10 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D81" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3545,10 +3560,10 @@
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D82" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3559,10 +3574,10 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D83" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3573,10 +3588,10 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D84" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3587,10 +3602,10 @@
         <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D85" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3601,10 +3616,10 @@
         <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D86" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3615,10 +3630,10 @@
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D87" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3629,10 +3644,10 @@
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D88" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3643,10 +3658,10 @@
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D89" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3654,10 +3669,10 @@
         <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D90" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3668,10 +3683,10 @@
         <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D91" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3682,10 +3697,10 @@
         <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D92" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3696,10 +3711,10 @@
         <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D93" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3710,10 +3725,10 @@
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D94" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3724,10 +3739,10 @@
         <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D95" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3738,10 +3753,10 @@
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D96" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3752,10 +3767,10 @@
         <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D97" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3766,10 +3781,10 @@
         <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D98" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3780,10 +3795,10 @@
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D99" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3791,10 +3806,10 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D100" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3805,10 +3820,10 @@
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D101" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3819,10 +3834,10 @@
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D102" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3833,10 +3848,10 @@
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D103" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3847,10 +3862,10 @@
         <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D104" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3858,10 +3873,10 @@
         <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D105" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3872,10 +3887,10 @@
         <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D106" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3883,10 +3898,10 @@
         <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D107" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3897,10 +3912,10 @@
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D108" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3911,10 +3926,10 @@
         <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D109" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3925,10 +3940,10 @@
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D110" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3939,10 +3954,10 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D111" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3953,10 +3968,10 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D112" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3964,10 +3979,10 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D113" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3975,10 +3990,10 @@
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D114" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3986,10 +4001,10 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D115" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3997,10 +4012,10 @@
         <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D116" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4011,10 +4026,10 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D117" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4025,10 +4040,10 @@
         <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D118" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4036,10 +4051,10 @@
         <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D119" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4047,10 +4062,10 @@
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D120" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4058,10 +4073,10 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D121" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4069,10 +4084,10 @@
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D122" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4080,10 +4095,10 @@
         <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D123" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4091,10 +4106,10 @@
         <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D124" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4105,10 +4120,10 @@
         <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D125" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4119,10 +4134,10 @@
         <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D126" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4133,10 +4148,10 @@
         <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D127" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4147,10 +4162,10 @@
         <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D128" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4161,10 +4176,10 @@
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D129" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4175,10 +4190,10 @@
         <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D130" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4189,10 +4204,10 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D131" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4203,10 +4218,10 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D132" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4217,10 +4232,10 @@
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D133" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4231,10 +4246,10 @@
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D134" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4245,10 +4260,10 @@
         <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D135" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4259,10 +4274,10 @@
         <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D136" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4273,10 +4288,10 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D137" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4287,10 +4302,10 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D138" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4301,10 +4316,10 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D139" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4315,10 +4330,10 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D140" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4329,10 +4344,10 @@
         <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D141" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4343,10 +4358,10 @@
         <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D142" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4357,10 +4372,10 @@
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D143" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4371,10 +4386,10 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D144" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4385,10 +4400,10 @@
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D145" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4399,10 +4414,10 @@
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D146" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4413,10 +4428,10 @@
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D147" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4427,10 +4442,10 @@
         <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D148" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4441,10 +4456,10 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D149" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4455,10 +4470,10 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D150" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4469,10 +4484,10 @@
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D151" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4483,10 +4498,10 @@
         <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D152" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4497,10 +4512,10 @@
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D153" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4511,10 +4526,10 @@
         <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D154" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4525,10 +4540,10 @@
         <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D155" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4539,10 +4554,10 @@
         <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D156" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4553,10 +4568,10 @@
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D157" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4567,10 +4582,10 @@
         <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D158" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4581,10 +4596,10 @@
         <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D159" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4595,10 +4610,10 @@
         <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D160" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4609,10 +4624,10 @@
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D161" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4623,10 +4638,10 @@
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D162" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4637,10 +4652,10 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D163" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4651,10 +4666,10 @@
         <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D164" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4665,10 +4680,10 @@
         <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D165" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4679,10 +4694,10 @@
         <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D166" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4693,10 +4708,10 @@
         <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D167" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4707,10 +4722,10 @@
         <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D168" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4721,10 +4736,10 @@
         <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D169" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4735,10 +4750,10 @@
         <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D170" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4749,10 +4764,10 @@
         <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D171" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4763,10 +4778,10 @@
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D172" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4777,10 +4792,10 @@
         <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D173" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4791,10 +4806,10 @@
         <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D174" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4805,10 +4820,10 @@
         <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D175" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4819,10 +4834,10 @@
         <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D176" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4833,10 +4848,10 @@
         <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D177" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4847,10 +4862,10 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D178" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4861,10 +4876,10 @@
         <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D179" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4875,10 +4890,10 @@
         <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D180" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4889,10 +4904,10 @@
         <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D181" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4903,10 +4918,10 @@
         <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D182" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4917,10 +4932,10 @@
         <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D183" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4931,10 +4946,10 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D184" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4945,10 +4960,10 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D185" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4959,10 +4974,10 @@
         <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D186" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4973,10 +4988,10 @@
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D187" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4987,10 +5002,10 @@
         <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D188" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5001,10 +5016,10 @@
         <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D189" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5015,10 +5030,10 @@
         <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D190" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5029,10 +5044,10 @@
         <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D191" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5043,10 +5058,10 @@
         <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D192" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5057,10 +5072,10 @@
         <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D193" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5071,10 +5086,10 @@
         <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D194" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5085,10 +5100,10 @@
         <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D195" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5099,10 +5114,10 @@
         <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D196" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5113,10 +5128,10 @@
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D197" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5127,10 +5142,10 @@
         <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D198" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5141,10 +5156,10 @@
         <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D199" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5155,10 +5170,10 @@
         <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D200" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5169,10 +5184,10 @@
         <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D201" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5183,10 +5198,10 @@
         <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D202" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5197,10 +5212,10 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D203" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5211,10 +5226,10 @@
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D204" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5225,10 +5240,10 @@
         <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D205" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5239,10 +5254,10 @@
         <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D206" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5253,10 +5268,10 @@
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D207" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5267,10 +5282,10 @@
         <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D208" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5281,10 +5296,10 @@
         <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D209" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5295,10 +5310,10 @@
         <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D210" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5309,10 +5324,10 @@
         <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D211" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5323,10 +5338,10 @@
         <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D212" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5337,10 +5352,10 @@
         <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D213" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5351,10 +5366,10 @@
         <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D214" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5365,10 +5380,10 @@
         <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D215" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5379,10 +5394,10 @@
         <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D216" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5393,10 +5408,10 @@
         <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D217" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5407,10 +5422,10 @@
         <v>222</v>
       </c>
       <c r="C218" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D218" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5421,10 +5436,10 @@
         <v>223</v>
       </c>
       <c r="C219" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D219" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5435,10 +5450,10 @@
         <v>224</v>
       </c>
       <c r="C220" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D220" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5449,10 +5464,10 @@
         <v>225</v>
       </c>
       <c r="C221" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D221" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5463,10 +5478,10 @@
         <v>226</v>
       </c>
       <c r="C222" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D222" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5477,10 +5492,10 @@
         <v>227</v>
       </c>
       <c r="C223" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D223" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5491,10 +5506,10 @@
         <v>228</v>
       </c>
       <c r="C224" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D224" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5505,10 +5520,10 @@
         <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D225" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5519,10 +5534,10 @@
         <v>230</v>
       </c>
       <c r="C226" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D226" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5532,8 +5547,11 @@
       <c r="B227" t="s">
         <v>231</v>
       </c>
+      <c r="C227" t="s">
+        <v>459</v>
+      </c>
       <c r="D227" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5543,8 +5561,25 @@
       <c r="B228" t="s">
         <v>232</v>
       </c>
+      <c r="C228" t="s">
+        <v>460</v>
+      </c>
       <c r="D228" t="s">
-        <v>684</v>
+        <v>688</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" t="s">
+        <v>4</v>
+      </c>
+      <c r="B229" t="s">
+        <v>233</v>
+      </c>
+      <c r="C229" t="s">
+        <v>461</v>
+      </c>
+      <c r="D229" t="s">
+        <v>689</v>
       </c>
     </row>
   </sheetData>

--- a/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
+++ b/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="696">
   <si>
     <t>THÔNG TIN KHO</t>
   </si>
@@ -718,6 +718,12 @@
     <t>A247</t>
   </si>
   <si>
+    <t>A215</t>
+  </si>
+  <si>
+    <t>A252</t>
+  </si>
+  <si>
     <t>-4776256360</t>
   </si>
   <si>
@@ -895,7 +901,7 @@
     <t>-5116235199</t>
   </si>
   <si>
-    <t>-5020576115</t>
+    <t>-1004427935189</t>
   </si>
   <si>
     <t>-5182777019</t>
@@ -1402,6 +1408,12 @@
     <t>-1004367466882</t>
   </si>
   <si>
+    <t>-1004387715043</t>
+  </si>
+  <si>
+    <t>-1004488038357</t>
+  </si>
+  <si>
     <t>KFM_BDU_DAN - 27 Tân Lập</t>
   </si>
   <si>
@@ -1579,7 +1591,7 @@
     <t>KFM_BDU_DAN - B2.01.05 Tháp B Opal Boulevard</t>
   </si>
   <si>
-    <t>KFM_HCM_Q07 - B1.01 Chung cư Golden Star</t>
+    <t>KFM_HCM_Q7 - A165 (Golden Star)</t>
   </si>
   <si>
     <t>KFM_HCM_Q07 - Block K Happy Valley</t>
@@ -2077,13 +2089,19 @@
     <t>KFM_HCM_BCH - D-2.01A Westgate An Gia</t>
   </si>
   <si>
-    <t>KFM_HCM_Q7 - A248 (Garden Plaza)</t>
-  </si>
-  <si>
-    <t>KFM_HCM_Q7 - A255 (Green View)</t>
+    <t>KFM_HCM_Q7 - DC - A248 (Garden Plaza)</t>
+  </si>
+  <si>
+    <t>KFM_HCM_Q7 - DC - A255 (Green View)</t>
   </si>
   <si>
     <t>KFM_HCM_BTA - DC - A247 (Lê Cơ)</t>
+  </si>
+  <si>
+    <t>KFM_HCM_Q12 - DC - A215 (Thạnh Xuân 14)</t>
+  </si>
+  <si>
+    <t>KFM_HCM_TDU - DC - A252 (DS9 An Khánh)</t>
   </si>
 </sst>
 </file>
@@ -2415,7 +2433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D229"/>
+  <dimension ref="A1:D231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2440,10 +2458,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2454,10 +2472,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D3" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2468,10 +2486,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D4" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2482,10 +2500,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D5" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2496,10 +2514,10 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D6" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2510,10 +2528,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D7" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2524,10 +2542,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D8" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2538,10 +2556,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D9" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2552,10 +2570,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D10" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2566,10 +2584,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D11" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2580,10 +2598,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D12" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2594,10 +2612,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D13" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2608,10 +2626,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D14" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2622,10 +2640,10 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D15" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2636,10 +2654,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D16" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2650,10 +2668,10 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D17" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2664,10 +2682,10 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D18" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2678,10 +2696,10 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D19" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2692,10 +2710,10 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D20" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2706,10 +2724,10 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D21" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2720,10 +2738,10 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D22" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2734,10 +2752,10 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D23" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2748,10 +2766,10 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D24" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2762,10 +2780,10 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2776,10 +2794,10 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D26" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2790,10 +2808,10 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2804,10 +2822,10 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D28" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2818,10 +2836,10 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D29" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2832,10 +2850,10 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D30" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2846,10 +2864,10 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2860,10 +2878,10 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D32" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2874,10 +2892,10 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D33" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2888,10 +2906,10 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D34" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2902,10 +2920,10 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D35" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2916,10 +2934,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D36" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2930,10 +2948,10 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D37" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2944,10 +2962,10 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D38" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2958,10 +2976,10 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D39" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2972,10 +2990,10 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D40" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2986,10 +3004,10 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D41" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3000,10 +3018,10 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D42" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3014,10 +3032,10 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D43" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3028,10 +3046,10 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D44" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3042,10 +3060,10 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D45" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3056,10 +3074,10 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D46" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3070,10 +3088,10 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D47" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3084,10 +3102,10 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D48" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3098,10 +3116,10 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D49" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3112,10 +3130,10 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D50" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3126,10 +3144,10 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D51" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3140,10 +3158,10 @@
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D52" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3154,10 +3172,10 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D53" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3168,10 +3186,10 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D54" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3182,10 +3200,10 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D55" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3196,10 +3214,10 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D56" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3210,10 +3228,10 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D57" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3224,10 +3242,10 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D58" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3238,10 +3256,10 @@
         <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D59" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3252,10 +3270,10 @@
         <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D60" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3266,10 +3284,10 @@
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D61" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3280,10 +3298,10 @@
         <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D62" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3294,10 +3312,10 @@
         <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D63" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3308,10 +3326,10 @@
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D64" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3322,10 +3340,10 @@
         <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D65" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3336,10 +3354,10 @@
         <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D66" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3350,10 +3368,10 @@
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D67" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3364,10 +3382,10 @@
         <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D68" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3378,10 +3396,10 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D69" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3392,10 +3410,10 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D70" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3406,10 +3424,10 @@
         <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D71" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3420,10 +3438,10 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D72" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3434,10 +3452,10 @@
         <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D73" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3448,10 +3466,10 @@
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D74" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3462,10 +3480,10 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D75" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3476,10 +3494,10 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D76" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3490,10 +3508,10 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D77" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3504,10 +3522,10 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D78" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3518,10 +3536,10 @@
         <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D79" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3532,10 +3550,10 @@
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D80" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3546,10 +3564,10 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D81" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3560,10 +3578,10 @@
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D82" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3574,10 +3592,10 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D83" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3588,10 +3606,10 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D84" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3602,10 +3620,10 @@
         <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D85" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3616,10 +3634,10 @@
         <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D86" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3630,10 +3648,10 @@
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D87" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3644,10 +3662,10 @@
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D88" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3658,10 +3676,10 @@
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D89" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3669,10 +3687,10 @@
         <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D90" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3683,10 +3701,10 @@
         <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D91" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3697,10 +3715,10 @@
         <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D92" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3711,10 +3729,10 @@
         <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D93" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3725,10 +3743,10 @@
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D94" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3739,10 +3757,10 @@
         <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D95" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3753,10 +3771,10 @@
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D96" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3767,10 +3785,10 @@
         <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D97" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3781,10 +3799,10 @@
         <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D98" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3795,10 +3813,10 @@
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D99" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3806,10 +3824,10 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D100" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3820,10 +3838,10 @@
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D101" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3834,10 +3852,10 @@
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D102" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3848,10 +3866,10 @@
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D103" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3862,10 +3880,10 @@
         <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D104" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3873,10 +3891,10 @@
         <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D105" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3887,10 +3905,10 @@
         <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D106" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3898,10 +3916,10 @@
         <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D107" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3912,10 +3930,10 @@
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D108" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3926,10 +3944,10 @@
         <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D109" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3940,10 +3958,10 @@
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D110" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3954,10 +3972,10 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D111" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3968,10 +3986,10 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D112" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3979,10 +3997,10 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D113" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3990,10 +4008,10 @@
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D114" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4001,10 +4019,10 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D115" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4012,10 +4030,10 @@
         <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D116" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4026,10 +4044,10 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D117" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4040,10 +4058,10 @@
         <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D118" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4051,10 +4069,10 @@
         <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D119" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4062,10 +4080,10 @@
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D120" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4073,10 +4091,10 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D121" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4084,10 +4102,10 @@
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D122" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4095,10 +4113,10 @@
         <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D123" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4106,10 +4124,10 @@
         <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D124" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4120,10 +4138,10 @@
         <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D125" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4134,10 +4152,10 @@
         <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D126" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4148,10 +4166,10 @@
         <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D127" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4162,10 +4180,10 @@
         <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D128" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4176,10 +4194,10 @@
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D129" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4190,10 +4208,10 @@
         <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D130" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4204,10 +4222,10 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D131" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4218,10 +4236,10 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D132" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4232,10 +4250,10 @@
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D133" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4246,10 +4264,10 @@
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D134" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4260,10 +4278,10 @@
         <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D135" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4274,10 +4292,10 @@
         <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D136" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4288,10 +4306,10 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D137" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4302,10 +4320,10 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D138" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4316,10 +4334,10 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D139" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4330,10 +4348,10 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D140" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4344,10 +4362,10 @@
         <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D141" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4358,10 +4376,10 @@
         <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D142" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4372,10 +4390,10 @@
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D143" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4386,10 +4404,10 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D144" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4400,10 +4418,10 @@
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D145" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4414,10 +4432,10 @@
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D146" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4428,10 +4446,10 @@
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D147" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4442,10 +4460,10 @@
         <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D148" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4456,10 +4474,10 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D149" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4470,10 +4488,10 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D150" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4484,10 +4502,10 @@
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D151" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4498,10 +4516,10 @@
         <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D152" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4512,10 +4530,10 @@
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D153" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4526,10 +4544,10 @@
         <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D154" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4540,10 +4558,10 @@
         <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D155" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4554,10 +4572,10 @@
         <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D156" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4568,10 +4586,10 @@
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D157" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4582,10 +4600,10 @@
         <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D158" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4596,10 +4614,10 @@
         <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D159" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4610,10 +4628,10 @@
         <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D160" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4624,10 +4642,10 @@
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D161" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4638,10 +4656,10 @@
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D162" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4652,10 +4670,10 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D163" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4666,10 +4684,10 @@
         <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D164" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4680,10 +4698,10 @@
         <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D165" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4694,10 +4712,10 @@
         <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D166" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4708,10 +4726,10 @@
         <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D167" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4722,10 +4740,10 @@
         <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D168" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4736,10 +4754,10 @@
         <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D169" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4750,10 +4768,10 @@
         <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D170" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4764,10 +4782,10 @@
         <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D171" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4778,10 +4796,10 @@
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D172" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4792,10 +4810,10 @@
         <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D173" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4806,10 +4824,10 @@
         <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D174" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4820,10 +4838,10 @@
         <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D175" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4834,10 +4852,10 @@
         <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D176" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4848,10 +4866,10 @@
         <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D177" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4862,10 +4880,10 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D178" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4876,10 +4894,10 @@
         <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D179" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4890,10 +4908,10 @@
         <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D180" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4904,10 +4922,10 @@
         <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D181" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4918,10 +4936,10 @@
         <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D182" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4932,10 +4950,10 @@
         <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D183" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4946,10 +4964,10 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D184" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4960,10 +4978,10 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D185" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4974,10 +4992,10 @@
         <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D186" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4988,10 +5006,10 @@
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D187" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5002,10 +5020,10 @@
         <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D188" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5016,10 +5034,10 @@
         <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D189" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5030,10 +5048,10 @@
         <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D190" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5044,10 +5062,10 @@
         <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D191" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5058,10 +5076,10 @@
         <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D192" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5072,10 +5090,10 @@
         <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D193" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5086,10 +5104,10 @@
         <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D194" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5100,10 +5118,10 @@
         <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D195" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5114,10 +5132,10 @@
         <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D196" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5128,10 +5146,10 @@
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D197" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5142,10 +5160,10 @@
         <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D198" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5156,10 +5174,10 @@
         <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D199" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5170,10 +5188,10 @@
         <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D200" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5184,10 +5202,10 @@
         <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D201" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5198,10 +5216,10 @@
         <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D202" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5212,10 +5230,10 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D203" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5226,10 +5244,10 @@
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D204" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5240,10 +5258,10 @@
         <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D205" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5254,10 +5272,10 @@
         <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D206" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5268,10 +5286,10 @@
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D207" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5282,10 +5300,10 @@
         <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D208" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5296,10 +5314,10 @@
         <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D209" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5310,10 +5328,10 @@
         <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D210" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5324,10 +5342,10 @@
         <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D211" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5338,10 +5356,10 @@
         <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D212" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5352,10 +5370,10 @@
         <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D213" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5366,10 +5384,10 @@
         <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D214" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5380,10 +5398,10 @@
         <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D215" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5394,10 +5412,10 @@
         <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D216" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5408,10 +5426,10 @@
         <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D217" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5422,10 +5440,10 @@
         <v>222</v>
       </c>
       <c r="C218" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D218" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5436,10 +5454,10 @@
         <v>223</v>
       </c>
       <c r="C219" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D219" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5450,10 +5468,10 @@
         <v>224</v>
       </c>
       <c r="C220" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D220" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5464,10 +5482,10 @@
         <v>225</v>
       </c>
       <c r="C221" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D221" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5478,10 +5496,10 @@
         <v>226</v>
       </c>
       <c r="C222" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D222" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5492,10 +5510,10 @@
         <v>227</v>
       </c>
       <c r="C223" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D223" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5506,10 +5524,10 @@
         <v>228</v>
       </c>
       <c r="C224" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D224" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5520,10 +5538,10 @@
         <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D225" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5534,10 +5552,10 @@
         <v>230</v>
       </c>
       <c r="C226" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D226" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5548,10 +5566,10 @@
         <v>231</v>
       </c>
       <c r="C227" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D227" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5562,10 +5580,10 @@
         <v>232</v>
       </c>
       <c r="C228" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D228" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5576,10 +5594,38 @@
         <v>233</v>
       </c>
       <c r="C229" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D229" t="s">
-        <v>689</v>
+        <v>693</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" t="s">
+        <v>4</v>
+      </c>
+      <c r="B230" t="s">
+        <v>234</v>
+      </c>
+      <c r="C230" t="s">
+        <v>464</v>
+      </c>
+      <c r="D230" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" t="s">
+        <v>4</v>
+      </c>
+      <c r="B231" t="s">
+        <v>235</v>
+      </c>
+      <c r="C231" t="s">
+        <v>465</v>
+      </c>
+      <c r="D231" t="s">
+        <v>695</v>
       </c>
     </row>
   </sheetData>

--- a/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
+++ b/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
@@ -1138,7 +1138,7 @@
     <t>-4201254758</t>
   </si>
   <si>
-    <t>-4987817070</t>
+    <t>-4783198151</t>
   </si>
   <si>
     <t>-869090413</t>

--- a/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
+++ b/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
@@ -901,7 +901,7 @@
     <t>-5116235199</t>
   </si>
   <si>
-    <t>-1004427935189</t>
+    <t>-5020576115</t>
   </si>
   <si>
     <t>-5182777019</t>
@@ -1591,7 +1591,7 @@
     <t>KFM_BDU_DAN - B2.01.05 Tháp B Opal Boulevard</t>
   </si>
   <si>
-    <t>KFM_HCM_Q7 - A165 (Golden Star)</t>
+    <t>KFM_HCM_Q07 - B1.01 Chung cư Golden Star</t>
   </si>
   <si>
     <t>KFM_HCM_Q07 - Block K Happy Valley</t>

--- a/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
+++ b/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="699">
   <si>
     <t>THÔNG TIN KHO</t>
   </si>
@@ -724,6 +724,9 @@
     <t>A252</t>
   </si>
   <si>
+    <t>A222</t>
+  </si>
+  <si>
     <t>-4776256360</t>
   </si>
   <si>
@@ -1174,7 +1177,7 @@
     <t>-4159767480</t>
   </si>
   <si>
-    <t>-4623899543</t>
+    <t>-4794317543</t>
   </si>
   <si>
     <t>-4221052636</t>
@@ -1414,6 +1417,9 @@
     <t>-1004488038357</t>
   </si>
   <si>
+    <t>-1004368025959</t>
+  </si>
+  <si>
     <t>KFM_BDU_DAN - 27 Tân Lập</t>
   </si>
   <si>
@@ -2102,6 +2108,9 @@
   </si>
   <si>
     <t>KFM_HCM_TDU - DC - A252 (DS9 An Khánh)</t>
+  </si>
+  <si>
+    <t>KFM_HCM_Q01 - Vinhomes Golden River</t>
   </si>
 </sst>
 </file>
@@ -2433,7 +2442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D231"/>
+  <dimension ref="A1:D232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2458,10 +2467,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2472,10 +2481,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2486,10 +2495,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D4" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2500,10 +2509,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D5" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2514,10 +2523,10 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D6" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2528,10 +2537,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D7" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2542,10 +2551,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D8" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2556,10 +2565,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D9" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2570,10 +2579,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D10" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2584,10 +2593,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D11" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2598,10 +2607,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D12" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2612,10 +2621,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D13" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2626,10 +2635,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D14" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2640,10 +2649,10 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D15" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2654,10 +2663,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D16" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2668,10 +2677,10 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D17" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2682,10 +2691,10 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D18" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2696,10 +2705,10 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D19" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2710,10 +2719,10 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D20" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2724,10 +2733,10 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D21" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2738,10 +2747,10 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D22" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2752,10 +2761,10 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D23" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2766,10 +2775,10 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2780,10 +2789,10 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D25" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2794,10 +2803,10 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2808,10 +2817,10 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D27" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2822,10 +2831,10 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D28" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2836,10 +2845,10 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D29" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2850,10 +2859,10 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D30" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2864,10 +2873,10 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2878,10 +2887,10 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D32" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2892,10 +2901,10 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D33" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2906,10 +2915,10 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D34" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2920,10 +2929,10 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D35" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2934,10 +2943,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D36" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2948,10 +2957,10 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D37" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2962,10 +2971,10 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D38" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2976,10 +2985,10 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D39" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2990,10 +2999,10 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D40" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3004,10 +3013,10 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D41" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3018,10 +3027,10 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D42" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3032,10 +3041,10 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D43" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3046,10 +3055,10 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D44" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3060,10 +3069,10 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D45" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3074,10 +3083,10 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D46" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3088,10 +3097,10 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D47" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3102,10 +3111,10 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D48" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3116,10 +3125,10 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D49" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3130,10 +3139,10 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D50" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3144,10 +3153,10 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D51" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3158,10 +3167,10 @@
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D52" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3172,10 +3181,10 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D53" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3186,10 +3195,10 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D54" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3200,10 +3209,10 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D55" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3214,10 +3223,10 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D56" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3228,10 +3237,10 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D57" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3242,10 +3251,10 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D58" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3256,10 +3265,10 @@
         <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D59" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3270,10 +3279,10 @@
         <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D60" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3284,10 +3293,10 @@
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D61" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3298,10 +3307,10 @@
         <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D62" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3312,10 +3321,10 @@
         <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D63" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3326,10 +3335,10 @@
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D64" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3340,10 +3349,10 @@
         <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D65" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3354,10 +3363,10 @@
         <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D66" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3368,10 +3377,10 @@
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D67" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3382,10 +3391,10 @@
         <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D68" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3396,10 +3405,10 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D69" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3410,10 +3419,10 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D70" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3424,10 +3433,10 @@
         <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D71" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3438,10 +3447,10 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D72" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3452,10 +3461,10 @@
         <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D73" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3466,10 +3475,10 @@
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D74" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3480,10 +3489,10 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D75" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3494,10 +3503,10 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D76" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3508,10 +3517,10 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D77" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3522,10 +3531,10 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D78" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3536,10 +3545,10 @@
         <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D79" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3550,10 +3559,10 @@
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D80" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3564,10 +3573,10 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D81" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3578,10 +3587,10 @@
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D82" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3592,10 +3601,10 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D83" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3606,10 +3615,10 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D84" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3620,10 +3629,10 @@
         <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D85" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3634,10 +3643,10 @@
         <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D86" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3648,10 +3657,10 @@
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D87" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3662,10 +3671,10 @@
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D88" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3676,10 +3685,10 @@
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D89" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3687,10 +3696,10 @@
         <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D90" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3701,10 +3710,10 @@
         <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D91" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3715,10 +3724,10 @@
         <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D92" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3729,10 +3738,10 @@
         <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D93" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3743,10 +3752,10 @@
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D94" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3757,10 +3766,10 @@
         <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D95" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3771,10 +3780,10 @@
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D96" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3785,10 +3794,10 @@
         <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D97" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3799,10 +3808,10 @@
         <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D98" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3813,10 +3822,10 @@
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D99" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3824,10 +3833,10 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D100" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3838,10 +3847,10 @@
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D101" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3852,10 +3861,10 @@
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D102" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3866,10 +3875,10 @@
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D103" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3880,10 +3889,10 @@
         <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D104" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3891,10 +3900,10 @@
         <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D105" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3905,10 +3914,10 @@
         <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D106" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3916,10 +3925,10 @@
         <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D107" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3930,10 +3939,10 @@
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D108" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3944,10 +3953,10 @@
         <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D109" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3958,10 +3967,10 @@
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D110" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3972,10 +3981,10 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D111" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3986,10 +3995,10 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D112" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3997,10 +4006,10 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D113" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4008,10 +4017,10 @@
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D114" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4019,10 +4028,10 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D115" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4030,10 +4039,10 @@
         <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D116" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4044,10 +4053,10 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D117" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4058,10 +4067,10 @@
         <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D118" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4069,10 +4078,10 @@
         <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D119" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4080,10 +4089,10 @@
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D120" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4091,10 +4100,10 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D121" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4102,10 +4111,10 @@
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D122" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4113,10 +4122,10 @@
         <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D123" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4124,10 +4133,10 @@
         <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D124" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4138,10 +4147,10 @@
         <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D125" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4152,10 +4161,10 @@
         <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D126" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4166,10 +4175,10 @@
         <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D127" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4180,10 +4189,10 @@
         <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D128" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4194,10 +4203,10 @@
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D129" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4208,10 +4217,10 @@
         <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D130" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4222,10 +4231,10 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D131" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4236,10 +4245,10 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D132" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4250,10 +4259,10 @@
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D133" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4264,10 +4273,10 @@
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D134" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4278,10 +4287,10 @@
         <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D135" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4292,10 +4301,10 @@
         <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D136" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4306,10 +4315,10 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D137" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4320,10 +4329,10 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D138" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4334,10 +4343,10 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D139" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4348,10 +4357,10 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D140" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4362,10 +4371,10 @@
         <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D141" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4376,10 +4385,10 @@
         <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D142" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4390,10 +4399,10 @@
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D143" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4404,10 +4413,10 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D144" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4418,10 +4427,10 @@
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D145" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4432,10 +4441,10 @@
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D146" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4446,10 +4455,10 @@
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D147" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4460,10 +4469,10 @@
         <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D148" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4474,10 +4483,10 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D149" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4488,10 +4497,10 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D150" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4502,10 +4511,10 @@
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D151" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4516,10 +4525,10 @@
         <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D152" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4530,10 +4539,10 @@
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D153" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4544,10 +4553,10 @@
         <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D154" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4558,10 +4567,10 @@
         <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D155" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4572,10 +4581,10 @@
         <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D156" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4586,10 +4595,10 @@
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D157" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4600,10 +4609,10 @@
         <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D158" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4614,10 +4623,10 @@
         <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D159" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4628,10 +4637,10 @@
         <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D160" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4642,10 +4651,10 @@
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D161" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4656,10 +4665,10 @@
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D162" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4670,10 +4679,10 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D163" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4684,10 +4693,10 @@
         <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D164" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4698,10 +4707,10 @@
         <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D165" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4712,10 +4721,10 @@
         <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D166" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4726,10 +4735,10 @@
         <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D167" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4740,10 +4749,10 @@
         <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D168" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4754,10 +4763,10 @@
         <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D169" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4768,10 +4777,10 @@
         <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D170" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4782,10 +4791,10 @@
         <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D171" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4796,10 +4805,10 @@
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D172" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4810,10 +4819,10 @@
         <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D173" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4824,10 +4833,10 @@
         <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D174" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4838,10 +4847,10 @@
         <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D175" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4852,10 +4861,10 @@
         <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D176" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4866,10 +4875,10 @@
         <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D177" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4880,10 +4889,10 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D178" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4894,10 +4903,10 @@
         <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D179" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4908,10 +4917,10 @@
         <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D180" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4922,10 +4931,10 @@
         <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D181" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4936,10 +4945,10 @@
         <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D182" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4950,10 +4959,10 @@
         <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D183" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4964,10 +4973,10 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D184" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4978,10 +4987,10 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D185" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4992,10 +5001,10 @@
         <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D186" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5006,10 +5015,10 @@
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D187" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5020,10 +5029,10 @@
         <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D188" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5034,10 +5043,10 @@
         <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D189" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5048,10 +5057,10 @@
         <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D190" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5062,10 +5071,10 @@
         <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D191" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5076,10 +5085,10 @@
         <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D192" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5090,10 +5099,10 @@
         <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D193" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5104,10 +5113,10 @@
         <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D194" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5118,10 +5127,10 @@
         <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D195" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5132,10 +5141,10 @@
         <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D196" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5146,10 +5155,10 @@
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D197" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5160,10 +5169,10 @@
         <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D198" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5174,10 +5183,10 @@
         <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D199" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5188,10 +5197,10 @@
         <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D200" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5202,10 +5211,10 @@
         <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D201" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5216,10 +5225,10 @@
         <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D202" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5230,10 +5239,10 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D203" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5244,10 +5253,10 @@
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D204" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5258,10 +5267,10 @@
         <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D205" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5272,10 +5281,10 @@
         <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D206" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5286,10 +5295,10 @@
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D207" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5300,10 +5309,10 @@
         <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D208" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5314,10 +5323,10 @@
         <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D209" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5328,10 +5337,10 @@
         <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D210" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5342,10 +5351,10 @@
         <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D211" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5356,10 +5365,10 @@
         <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D212" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5370,10 +5379,10 @@
         <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D213" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5384,10 +5393,10 @@
         <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D214" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5398,10 +5407,10 @@
         <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D215" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5412,10 +5421,10 @@
         <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D216" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5426,10 +5435,10 @@
         <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D217" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5440,10 +5449,10 @@
         <v>222</v>
       </c>
       <c r="C218" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D218" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5454,10 +5463,10 @@
         <v>223</v>
       </c>
       <c r="C219" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D219" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5468,10 +5477,10 @@
         <v>224</v>
       </c>
       <c r="C220" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D220" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5482,10 +5491,10 @@
         <v>225</v>
       </c>
       <c r="C221" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D221" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5496,10 +5505,10 @@
         <v>226</v>
       </c>
       <c r="C222" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D222" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5510,10 +5519,10 @@
         <v>227</v>
       </c>
       <c r="C223" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D223" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5524,10 +5533,10 @@
         <v>228</v>
       </c>
       <c r="C224" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D224" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5538,10 +5547,10 @@
         <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D225" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5552,10 +5561,10 @@
         <v>230</v>
       </c>
       <c r="C226" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D226" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5566,10 +5575,10 @@
         <v>231</v>
       </c>
       <c r="C227" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D227" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5580,10 +5589,10 @@
         <v>232</v>
       </c>
       <c r="C228" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D228" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5594,10 +5603,10 @@
         <v>233</v>
       </c>
       <c r="C229" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D229" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5608,10 +5617,10 @@
         <v>234</v>
       </c>
       <c r="C230" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D230" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5622,10 +5631,24 @@
         <v>235</v>
       </c>
       <c r="C231" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D231" t="s">
-        <v>695</v>
+        <v>697</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" t="s">
+        <v>4</v>
+      </c>
+      <c r="B232" t="s">
+        <v>236</v>
+      </c>
+      <c r="C232" t="s">
+        <v>467</v>
+      </c>
+      <c r="D232" t="s">
+        <v>698</v>
       </c>
     </row>
   </sheetData>

--- a/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
+++ b/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="702">
   <si>
     <t>THÔNG TIN KHO</t>
   </si>
@@ -727,6 +727,9 @@
     <t>A222</t>
   </si>
   <si>
+    <t>A259</t>
+  </si>
+  <si>
     <t>-4776256360</t>
   </si>
   <si>
@@ -1420,6 +1423,9 @@
     <t>-1004368025959</t>
   </si>
   <si>
+    <t>-1004469485931</t>
+  </si>
+  <si>
     <t>KFM_BDU_DAN - 27 Tân Lập</t>
   </si>
   <si>
@@ -2111,6 +2117,9 @@
   </si>
   <si>
     <t>KFM_HCM_Q01 - Vinhomes Golden River</t>
+  </si>
+  <si>
+    <t>KFM_BDU_TAN - 275 D33 KDC Viet Sing</t>
   </si>
 </sst>
 </file>
@@ -2442,7 +2451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D232"/>
+  <dimension ref="A1:D233"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2467,10 +2476,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2481,10 +2490,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2495,10 +2504,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D4" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2509,10 +2518,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D5" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2523,10 +2532,10 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D6" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2537,10 +2546,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D7" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2551,10 +2560,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D8" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2565,10 +2574,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D9" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2579,10 +2588,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D10" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2593,10 +2602,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D11" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2607,10 +2616,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D12" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2621,10 +2630,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D13" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2635,10 +2644,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D14" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2649,10 +2658,10 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2663,10 +2672,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D16" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2677,10 +2686,10 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D17" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2691,10 +2700,10 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D18" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2705,10 +2714,10 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D19" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2719,10 +2728,10 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D20" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2733,10 +2742,10 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D21" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2747,10 +2756,10 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D22" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2761,10 +2770,10 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D23" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2775,10 +2784,10 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D24" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2789,10 +2798,10 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2803,10 +2812,10 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D26" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2817,10 +2826,10 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D27" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2831,10 +2840,10 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D28" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2845,10 +2854,10 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D29" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2859,10 +2868,10 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2873,10 +2882,10 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D31" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2887,10 +2896,10 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D32" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2901,10 +2910,10 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D33" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2915,10 +2924,10 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D34" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2929,10 +2938,10 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D35" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2943,10 +2952,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D36" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2957,10 +2966,10 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D37" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2971,10 +2980,10 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D38" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2985,10 +2994,10 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D39" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2999,10 +3008,10 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D40" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3013,10 +3022,10 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D41" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3027,10 +3036,10 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D42" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3041,10 +3050,10 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D43" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3055,10 +3064,10 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D44" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3069,10 +3078,10 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D45" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3083,10 +3092,10 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D46" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3097,10 +3106,10 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D47" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3111,10 +3120,10 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D48" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3125,10 +3134,10 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D49" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3139,10 +3148,10 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D50" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3153,10 +3162,10 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D51" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3167,10 +3176,10 @@
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D52" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3181,10 +3190,10 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D53" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3195,10 +3204,10 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D54" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3209,10 +3218,10 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D55" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3223,10 +3232,10 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D56" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3237,10 +3246,10 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D57" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3251,10 +3260,10 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D58" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3265,10 +3274,10 @@
         <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D59" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3279,10 +3288,10 @@
         <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D60" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3293,10 +3302,10 @@
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D61" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3307,10 +3316,10 @@
         <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D62" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3321,10 +3330,10 @@
         <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D63" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3335,10 +3344,10 @@
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D64" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3349,10 +3358,10 @@
         <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D65" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3363,10 +3372,10 @@
         <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D66" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3377,10 +3386,10 @@
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D67" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3391,10 +3400,10 @@
         <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D68" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3405,10 +3414,10 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D69" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3419,10 +3428,10 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D70" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3433,10 +3442,10 @@
         <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D71" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3447,10 +3456,10 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D72" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3461,10 +3470,10 @@
         <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D73" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3475,10 +3484,10 @@
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D74" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3489,10 +3498,10 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D75" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3503,10 +3512,10 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D76" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3517,10 +3526,10 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D77" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3531,10 +3540,10 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D78" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3545,10 +3554,10 @@
         <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D79" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3559,10 +3568,10 @@
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D80" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3573,10 +3582,10 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D81" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3587,10 +3596,10 @@
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D82" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3601,10 +3610,10 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D83" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3615,10 +3624,10 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D84" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3629,10 +3638,10 @@
         <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D85" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3643,10 +3652,10 @@
         <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D86" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3657,10 +3666,10 @@
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D87" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3671,10 +3680,10 @@
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D88" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3685,10 +3694,10 @@
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D89" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3696,10 +3705,10 @@
         <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D90" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3710,10 +3719,10 @@
         <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D91" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3724,10 +3733,10 @@
         <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D92" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3738,10 +3747,10 @@
         <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D93" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3752,10 +3761,10 @@
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D94" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3766,10 +3775,10 @@
         <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D95" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3780,10 +3789,10 @@
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D96" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3794,10 +3803,10 @@
         <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D97" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3808,10 +3817,10 @@
         <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D98" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3822,10 +3831,10 @@
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D99" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3833,10 +3842,10 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D100" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3847,10 +3856,10 @@
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D101" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3861,10 +3870,10 @@
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D102" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3875,10 +3884,10 @@
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D103" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3889,10 +3898,10 @@
         <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D104" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3900,10 +3909,10 @@
         <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D105" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3914,10 +3923,10 @@
         <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D106" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3925,10 +3934,10 @@
         <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D107" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3939,10 +3948,10 @@
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D108" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3953,10 +3962,10 @@
         <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D109" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3967,10 +3976,10 @@
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D110" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3981,10 +3990,10 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D111" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3995,10 +4004,10 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D112" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4006,10 +4015,10 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D113" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4017,10 +4026,10 @@
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D114" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4028,10 +4037,10 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D115" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4039,10 +4048,10 @@
         <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D116" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4053,10 +4062,10 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D117" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4067,10 +4076,10 @@
         <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D118" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4078,10 +4087,10 @@
         <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D119" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4089,10 +4098,10 @@
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D120" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4100,10 +4109,10 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D121" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4111,10 +4120,10 @@
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D122" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4122,10 +4131,10 @@
         <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D123" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4133,10 +4142,10 @@
         <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D124" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4147,10 +4156,10 @@
         <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D125" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4161,10 +4170,10 @@
         <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D126" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4175,10 +4184,10 @@
         <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D127" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4189,10 +4198,10 @@
         <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D128" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4203,10 +4212,10 @@
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D129" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4217,10 +4226,10 @@
         <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D130" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4231,10 +4240,10 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D131" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4245,10 +4254,10 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D132" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4259,10 +4268,10 @@
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D133" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4273,10 +4282,10 @@
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D134" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4287,10 +4296,10 @@
         <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D135" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4301,10 +4310,10 @@
         <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D136" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4315,10 +4324,10 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D137" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4329,10 +4338,10 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D138" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4343,10 +4352,10 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D139" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4357,10 +4366,10 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D140" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4371,10 +4380,10 @@
         <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D141" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4385,10 +4394,10 @@
         <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D142" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4399,10 +4408,10 @@
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D143" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4413,10 +4422,10 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D144" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4427,10 +4436,10 @@
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D145" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4441,10 +4450,10 @@
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D146" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4455,10 +4464,10 @@
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D147" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4469,10 +4478,10 @@
         <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D148" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4483,10 +4492,10 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D149" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4497,10 +4506,10 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D150" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4511,10 +4520,10 @@
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D151" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4525,10 +4534,10 @@
         <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D152" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4539,10 +4548,10 @@
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D153" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4553,10 +4562,10 @@
         <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D154" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4567,10 +4576,10 @@
         <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D155" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4581,10 +4590,10 @@
         <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D156" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4595,10 +4604,10 @@
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D157" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4609,10 +4618,10 @@
         <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D158" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4623,10 +4632,10 @@
         <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D159" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4637,10 +4646,10 @@
         <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D160" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4651,10 +4660,10 @@
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D161" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4665,10 +4674,10 @@
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D162" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4679,10 +4688,10 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D163" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4693,10 +4702,10 @@
         <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D164" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4707,10 +4716,10 @@
         <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D165" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4721,10 +4730,10 @@
         <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D166" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4735,10 +4744,10 @@
         <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D167" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4749,10 +4758,10 @@
         <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D168" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4763,10 +4772,10 @@
         <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D169" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4777,10 +4786,10 @@
         <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D170" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4791,10 +4800,10 @@
         <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D171" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4805,10 +4814,10 @@
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D172" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4819,10 +4828,10 @@
         <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D173" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4833,10 +4842,10 @@
         <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D174" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4847,10 +4856,10 @@
         <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D175" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4861,10 +4870,10 @@
         <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D176" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4875,10 +4884,10 @@
         <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D177" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4889,10 +4898,10 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D178" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4903,10 +4912,10 @@
         <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D179" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4917,10 +4926,10 @@
         <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D180" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4931,10 +4940,10 @@
         <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D181" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4945,10 +4954,10 @@
         <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D182" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4959,10 +4968,10 @@
         <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D183" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4973,10 +4982,10 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D184" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4987,10 +4996,10 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D185" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5001,10 +5010,10 @@
         <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D186" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5015,10 +5024,10 @@
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D187" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5029,10 +5038,10 @@
         <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D188" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5043,10 +5052,10 @@
         <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D189" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5057,10 +5066,10 @@
         <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D190" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5071,10 +5080,10 @@
         <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D191" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5085,10 +5094,10 @@
         <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D192" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5099,10 +5108,10 @@
         <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D193" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5113,10 +5122,10 @@
         <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D194" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5127,10 +5136,10 @@
         <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D195" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5141,10 +5150,10 @@
         <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D196" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5155,10 +5164,10 @@
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D197" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5169,10 +5178,10 @@
         <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D198" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5183,10 +5192,10 @@
         <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D199" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5197,10 +5206,10 @@
         <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D200" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5211,10 +5220,10 @@
         <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D201" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5225,10 +5234,10 @@
         <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D202" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5239,10 +5248,10 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D203" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5253,10 +5262,10 @@
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D204" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5267,10 +5276,10 @@
         <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D205" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5281,10 +5290,10 @@
         <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D206" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5295,10 +5304,10 @@
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D207" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5309,10 +5318,10 @@
         <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D208" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5323,10 +5332,10 @@
         <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D209" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5337,10 +5346,10 @@
         <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D210" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5351,10 +5360,10 @@
         <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D211" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5365,10 +5374,10 @@
         <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D212" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5379,10 +5388,10 @@
         <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D213" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5393,10 +5402,10 @@
         <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D214" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5407,10 +5416,10 @@
         <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D215" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5421,10 +5430,10 @@
         <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D216" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5435,10 +5444,10 @@
         <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D217" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5449,10 +5458,10 @@
         <v>222</v>
       </c>
       <c r="C218" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D218" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5463,10 +5472,10 @@
         <v>223</v>
       </c>
       <c r="C219" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D219" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5477,10 +5486,10 @@
         <v>224</v>
       </c>
       <c r="C220" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D220" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5491,10 +5500,10 @@
         <v>225</v>
       </c>
       <c r="C221" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D221" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5505,10 +5514,10 @@
         <v>226</v>
       </c>
       <c r="C222" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D222" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5519,10 +5528,10 @@
         <v>227</v>
       </c>
       <c r="C223" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D223" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5533,10 +5542,10 @@
         <v>228</v>
       </c>
       <c r="C224" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D224" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5547,10 +5556,10 @@
         <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D225" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5561,10 +5570,10 @@
         <v>230</v>
       </c>
       <c r="C226" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D226" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5575,10 +5584,10 @@
         <v>231</v>
       </c>
       <c r="C227" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D227" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5589,10 +5598,10 @@
         <v>232</v>
       </c>
       <c r="C228" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D228" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5603,10 +5612,10 @@
         <v>233</v>
       </c>
       <c r="C229" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D229" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5617,10 +5626,10 @@
         <v>234</v>
       </c>
       <c r="C230" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D230" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5631,10 +5640,10 @@
         <v>235</v>
       </c>
       <c r="C231" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D231" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5645,10 +5654,24 @@
         <v>236</v>
       </c>
       <c r="C232" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D232" t="s">
-        <v>698</v>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" t="s">
+        <v>4</v>
+      </c>
+      <c r="B233" t="s">
+        <v>237</v>
+      </c>
+      <c r="C233" t="s">
+        <v>469</v>
+      </c>
+      <c r="D233" t="s">
+        <v>701</v>
       </c>
     </row>
   </sheetData>

--- a/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
+++ b/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="706">
   <si>
     <t>THÔNG TIN KHO</t>
   </si>
@@ -730,6 +730,12 @@
     <t>A259</t>
   </si>
   <si>
+    <t>A246</t>
+  </si>
+  <si>
+    <t>A258</t>
+  </si>
+  <si>
     <t>-4776256360</t>
   </si>
   <si>
@@ -1424,6 +1430,12 @@
   </si>
   <si>
     <t>-1004469485931</t>
+  </si>
+  <si>
+    <t>-1003957832728</t>
+  </si>
+  <si>
+    <t>-1004327654400</t>
   </si>
   <si>
     <t>KFM_BDU_DAN - 27 Tân Lập</t>
@@ -2451,7 +2463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D233"/>
+  <dimension ref="A1:D235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2476,10 +2488,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2490,10 +2502,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D3" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2504,10 +2516,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D4" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2518,10 +2530,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D5" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2532,10 +2544,10 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D6" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2546,10 +2558,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D7" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2560,10 +2572,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2574,10 +2586,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D9" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2588,10 +2600,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D10" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2602,10 +2614,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D11" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2616,10 +2628,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D12" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2630,10 +2642,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D13" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2644,10 +2656,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D14" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2658,10 +2670,10 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D15" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2672,10 +2684,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D16" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2686,10 +2698,10 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D17" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2700,10 +2712,10 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D18" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2714,10 +2726,10 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D19" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2728,10 +2740,10 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D20" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2742,10 +2754,10 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2756,10 +2768,10 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D22" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2770,10 +2782,10 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D23" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2784,10 +2796,10 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D24" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2798,10 +2810,10 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D25" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2812,10 +2824,10 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D26" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2826,10 +2838,10 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D27" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2840,10 +2852,10 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2854,10 +2866,10 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D29" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2868,10 +2880,10 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D30" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2882,10 +2894,10 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D31" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2896,10 +2908,10 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D32" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2910,10 +2922,10 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D33" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2924,10 +2936,10 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D34" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2938,10 +2950,10 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D35" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2952,10 +2964,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D36" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2966,10 +2978,10 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D37" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2980,10 +2992,10 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D38" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2994,10 +3006,10 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D39" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3008,10 +3020,10 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D40" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3022,10 +3034,10 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D41" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3036,10 +3048,10 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D42" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3050,10 +3062,10 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D43" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3064,10 +3076,10 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D44" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3078,10 +3090,10 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D45" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3092,10 +3104,10 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D46" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3106,10 +3118,10 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D47" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3120,10 +3132,10 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D48" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3134,10 +3146,10 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D49" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3148,10 +3160,10 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D50" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3162,10 +3174,10 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D51" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3176,10 +3188,10 @@
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D52" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3190,10 +3202,10 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D53" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3204,10 +3216,10 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D54" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3218,10 +3230,10 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D55" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3232,10 +3244,10 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D56" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3246,10 +3258,10 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D57" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3260,10 +3272,10 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D58" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3274,10 +3286,10 @@
         <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D59" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3288,10 +3300,10 @@
         <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D60" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3302,10 +3314,10 @@
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D61" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3316,10 +3328,10 @@
         <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D62" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3330,10 +3342,10 @@
         <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D63" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3344,10 +3356,10 @@
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D64" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3358,10 +3370,10 @@
         <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D65" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3372,10 +3384,10 @@
         <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D66" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3386,10 +3398,10 @@
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D67" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3400,10 +3412,10 @@
         <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D68" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3414,10 +3426,10 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D69" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3428,10 +3440,10 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D70" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3442,10 +3454,10 @@
         <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D71" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3456,10 +3468,10 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D72" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3470,10 +3482,10 @@
         <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D73" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3484,10 +3496,10 @@
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D74" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3498,10 +3510,10 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D75" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3512,10 +3524,10 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D76" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3526,10 +3538,10 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D77" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3540,10 +3552,10 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D78" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3554,10 +3566,10 @@
         <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D79" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3568,10 +3580,10 @@
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D80" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3582,10 +3594,10 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D81" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3596,10 +3608,10 @@
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D82" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3610,10 +3622,10 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D83" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3624,10 +3636,10 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D84" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3638,10 +3650,10 @@
         <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D85" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3652,10 +3664,10 @@
         <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D86" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3666,10 +3678,10 @@
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D87" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3680,10 +3692,10 @@
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D88" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3694,10 +3706,10 @@
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D89" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3705,10 +3717,10 @@
         <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D90" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3719,10 +3731,10 @@
         <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D91" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3733,10 +3745,10 @@
         <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D92" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3747,10 +3759,10 @@
         <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D93" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3761,10 +3773,10 @@
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D94" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3775,10 +3787,10 @@
         <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D95" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3789,10 +3801,10 @@
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D96" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3803,10 +3815,10 @@
         <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D97" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3817,10 +3829,10 @@
         <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D98" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3831,10 +3843,10 @@
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D99" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3842,10 +3854,10 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D100" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3856,10 +3868,10 @@
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D101" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3870,10 +3882,10 @@
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D102" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3884,10 +3896,10 @@
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D103" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3898,10 +3910,10 @@
         <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D104" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3909,10 +3921,10 @@
         <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D105" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3923,10 +3935,10 @@
         <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D106" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3934,10 +3946,10 @@
         <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D107" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3948,10 +3960,10 @@
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D108" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3962,10 +3974,10 @@
         <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D109" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3976,10 +3988,10 @@
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D110" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3990,10 +4002,10 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D111" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4004,10 +4016,10 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D112" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4015,10 +4027,10 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D113" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4026,10 +4038,10 @@
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D114" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4037,10 +4049,10 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D115" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4048,10 +4060,10 @@
         <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D116" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4062,10 +4074,10 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D117" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4076,10 +4088,10 @@
         <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D118" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4087,10 +4099,10 @@
         <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D119" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4098,10 +4110,10 @@
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D120" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4109,10 +4121,10 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D121" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4120,10 +4132,10 @@
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D122" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4131,10 +4143,10 @@
         <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D123" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4142,10 +4154,10 @@
         <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D124" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4156,10 +4168,10 @@
         <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D125" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4170,10 +4182,10 @@
         <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D126" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4184,10 +4196,10 @@
         <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D127" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4198,10 +4210,10 @@
         <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D128" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4212,10 +4224,10 @@
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D129" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4226,10 +4238,10 @@
         <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D130" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4240,10 +4252,10 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D131" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4254,10 +4266,10 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D132" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4268,10 +4280,10 @@
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D133" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4282,10 +4294,10 @@
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D134" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4296,10 +4308,10 @@
         <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D135" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4310,10 +4322,10 @@
         <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D136" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4324,10 +4336,10 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D137" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4338,10 +4350,10 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D138" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4352,10 +4364,10 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D139" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4366,10 +4378,10 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D140" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4380,10 +4392,10 @@
         <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D141" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4394,10 +4406,10 @@
         <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D142" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4408,10 +4420,10 @@
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D143" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4422,10 +4434,10 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D144" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4436,10 +4448,10 @@
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D145" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4450,10 +4462,10 @@
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D146" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4464,10 +4476,10 @@
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D147" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4478,10 +4490,10 @@
         <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D148" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4492,10 +4504,10 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D149" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4506,10 +4518,10 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D150" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4520,10 +4532,10 @@
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D151" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4534,10 +4546,10 @@
         <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D152" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4548,10 +4560,10 @@
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D153" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4562,10 +4574,10 @@
         <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D154" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4576,10 +4588,10 @@
         <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D155" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4590,10 +4602,10 @@
         <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D156" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4604,10 +4616,10 @@
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D157" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4618,10 +4630,10 @@
         <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D158" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4632,10 +4644,10 @@
         <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D159" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4646,10 +4658,10 @@
         <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D160" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4660,10 +4672,10 @@
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D161" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4674,10 +4686,10 @@
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D162" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4688,10 +4700,10 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D163" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4702,10 +4714,10 @@
         <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D164" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4716,10 +4728,10 @@
         <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D165" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4730,10 +4742,10 @@
         <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D166" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4744,10 +4756,10 @@
         <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D167" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4758,10 +4770,10 @@
         <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D168" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4772,10 +4784,10 @@
         <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D169" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4786,10 +4798,10 @@
         <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D170" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4800,10 +4812,10 @@
         <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D171" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4814,10 +4826,10 @@
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D172" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4828,10 +4840,10 @@
         <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D173" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4842,10 +4854,10 @@
         <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D174" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4856,10 +4868,10 @@
         <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D175" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4870,10 +4882,10 @@
         <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D176" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4884,10 +4896,10 @@
         <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D177" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4898,10 +4910,10 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D178" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4912,10 +4924,10 @@
         <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D179" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4926,10 +4938,10 @@
         <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D180" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4940,10 +4952,10 @@
         <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D181" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4954,10 +4966,10 @@
         <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D182" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4968,10 +4980,10 @@
         <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D183" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4982,10 +4994,10 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D184" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4996,10 +5008,10 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D185" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5010,10 +5022,10 @@
         <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D186" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5024,10 +5036,10 @@
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D187" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5038,10 +5050,10 @@
         <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D188" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5052,10 +5064,10 @@
         <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D189" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5066,10 +5078,10 @@
         <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D190" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5080,10 +5092,10 @@
         <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D191" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5094,10 +5106,10 @@
         <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D192" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5108,10 +5120,10 @@
         <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D193" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5122,10 +5134,10 @@
         <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D194" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5136,10 +5148,10 @@
         <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D195" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5150,10 +5162,10 @@
         <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D196" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5164,10 +5176,10 @@
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D197" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5178,10 +5190,10 @@
         <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D198" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5192,10 +5204,10 @@
         <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D199" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5206,10 +5218,10 @@
         <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D200" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5220,10 +5232,10 @@
         <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D201" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5234,10 +5246,10 @@
         <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D202" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5248,10 +5260,10 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D203" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5262,10 +5274,10 @@
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D204" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5276,10 +5288,10 @@
         <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D205" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5290,10 +5302,10 @@
         <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D206" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5304,10 +5316,10 @@
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D207" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5318,10 +5330,10 @@
         <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D208" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5332,10 +5344,10 @@
         <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D209" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5346,10 +5358,10 @@
         <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D210" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5360,10 +5372,10 @@
         <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D211" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5374,10 +5386,10 @@
         <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D212" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5388,10 +5400,10 @@
         <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D213" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5402,10 +5414,10 @@
         <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D214" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5416,10 +5428,10 @@
         <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D215" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5430,10 +5442,10 @@
         <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D216" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5444,10 +5456,10 @@
         <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D217" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5458,10 +5470,10 @@
         <v>222</v>
       </c>
       <c r="C218" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D218" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5472,10 +5484,10 @@
         <v>223</v>
       </c>
       <c r="C219" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D219" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5486,10 +5498,10 @@
         <v>224</v>
       </c>
       <c r="C220" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D220" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5500,10 +5512,10 @@
         <v>225</v>
       </c>
       <c r="C221" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D221" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5514,10 +5526,10 @@
         <v>226</v>
       </c>
       <c r="C222" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D222" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5528,10 +5540,10 @@
         <v>227</v>
       </c>
       <c r="C223" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D223" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5542,10 +5554,10 @@
         <v>228</v>
       </c>
       <c r="C224" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D224" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5556,10 +5568,10 @@
         <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D225" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5570,10 +5582,10 @@
         <v>230</v>
       </c>
       <c r="C226" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D226" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5584,10 +5596,10 @@
         <v>231</v>
       </c>
       <c r="C227" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D227" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5598,10 +5610,10 @@
         <v>232</v>
       </c>
       <c r="C228" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D228" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5612,10 +5624,10 @@
         <v>233</v>
       </c>
       <c r="C229" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D229" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5626,10 +5638,10 @@
         <v>234</v>
       </c>
       <c r="C230" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D230" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5640,10 +5652,10 @@
         <v>235</v>
       </c>
       <c r="C231" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D231" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5654,10 +5666,10 @@
         <v>236</v>
       </c>
       <c r="C232" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D232" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5668,10 +5680,38 @@
         <v>237</v>
       </c>
       <c r="C233" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D233" t="s">
-        <v>701</v>
+        <v>705</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" t="s">
+        <v>4</v>
+      </c>
+      <c r="B234" t="s">
+        <v>238</v>
+      </c>
+      <c r="C234" t="s">
+        <v>472</v>
+      </c>
+      <c r="D234" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" t="s">
+        <v>4</v>
+      </c>
+      <c r="B235" t="s">
+        <v>239</v>
+      </c>
+      <c r="C235" t="s">
+        <v>473</v>
+      </c>
+      <c r="D235" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
+++ b/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
@@ -1237,7 +1237,7 @@
     <t>-4879450613</t>
   </si>
   <si>
-    <t>-4187036269</t>
+    <t>-1004451611911</t>
   </si>
   <si>
     <t>-4676492169</t>

--- a/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
+++ b/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="709">
   <si>
     <t>THÔNG TIN KHO</t>
   </si>
@@ -736,6 +736,9 @@
     <t>A258</t>
   </si>
   <si>
+    <t>B001</t>
+  </si>
+  <si>
     <t>-4776256360</t>
   </si>
   <si>
@@ -1438,6 +1441,9 @@
     <t>-1004327654400</t>
   </si>
   <si>
+    <t>-1004305022913</t>
+  </si>
+  <si>
     <t>KFM_BDU_DAN - 27 Tân Lập</t>
   </si>
   <si>
@@ -2132,6 +2138,9 @@
   </si>
   <si>
     <t>KFM_BDU_TAN - 275 D33 KDC Viet Sing</t>
+  </si>
+  <si>
+    <t>KFM_HNI_YHO - CT3 Yên Hoà Park View</t>
   </si>
 </sst>
 </file>
@@ -2463,7 +2472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D235"/>
+  <dimension ref="A1:D236"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2488,10 +2497,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2502,10 +2511,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2516,10 +2525,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D4" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2530,10 +2539,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D5" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2544,10 +2553,10 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2558,10 +2567,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D7" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D8" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2586,10 +2595,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D9" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2600,10 +2609,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D10" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2614,10 +2623,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D11" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2628,10 +2637,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D12" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2642,10 +2651,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D13" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2656,10 +2665,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D14" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2670,10 +2679,10 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D15" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2684,10 +2693,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D16" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2698,10 +2707,10 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D17" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2712,10 +2721,10 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D18" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2726,10 +2735,10 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D19" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2740,10 +2749,10 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D20" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2754,10 +2763,10 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D21" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2768,10 +2777,10 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D22" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2782,10 +2791,10 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2796,10 +2805,10 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D24" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2810,10 +2819,10 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2824,10 +2833,10 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D26" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2838,10 +2847,10 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2852,10 +2861,10 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D28" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2866,10 +2875,10 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D29" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2880,10 +2889,10 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D30" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2894,10 +2903,10 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D31" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2908,10 +2917,10 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D32" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2922,10 +2931,10 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D33" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2936,10 +2945,10 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D34" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2950,10 +2959,10 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D35" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2964,10 +2973,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D36" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2978,10 +2987,10 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D37" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2992,10 +3001,10 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D38" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3006,10 +3015,10 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D39" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3020,10 +3029,10 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D40" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3034,10 +3043,10 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D41" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3048,10 +3057,10 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D42" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3062,10 +3071,10 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D43" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3076,10 +3085,10 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D44" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3090,10 +3099,10 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D45" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3104,10 +3113,10 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D46" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3118,10 +3127,10 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D47" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3132,10 +3141,10 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D48" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3146,10 +3155,10 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D49" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3160,10 +3169,10 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D50" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3174,10 +3183,10 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D51" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3188,10 +3197,10 @@
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D52" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3202,10 +3211,10 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D53" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3216,10 +3225,10 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D54" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3230,10 +3239,10 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D55" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3244,10 +3253,10 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D56" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3258,10 +3267,10 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D57" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3272,10 +3281,10 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D58" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3286,10 +3295,10 @@
         <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D59" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3300,10 +3309,10 @@
         <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D60" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3314,10 +3323,10 @@
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D61" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3328,10 +3337,10 @@
         <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D62" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3342,10 +3351,10 @@
         <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D63" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3356,10 +3365,10 @@
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D64" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3370,10 +3379,10 @@
         <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D65" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3384,10 +3393,10 @@
         <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D66" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3398,10 +3407,10 @@
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D67" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3412,10 +3421,10 @@
         <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D68" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3426,10 +3435,10 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D69" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3440,10 +3449,10 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D70" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3454,10 +3463,10 @@
         <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D71" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3468,10 +3477,10 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D72" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3482,10 +3491,10 @@
         <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D73" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3496,10 +3505,10 @@
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D74" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3510,10 +3519,10 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D75" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3524,10 +3533,10 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D76" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3538,10 +3547,10 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D77" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3552,10 +3561,10 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D78" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3566,10 +3575,10 @@
         <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D79" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D80" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D81" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3608,10 +3617,10 @@
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D82" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3622,10 +3631,10 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D83" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3636,10 +3645,10 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D84" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3650,10 +3659,10 @@
         <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D85" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3664,10 +3673,10 @@
         <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D86" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3678,10 +3687,10 @@
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D87" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3692,10 +3701,10 @@
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D88" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3706,10 +3715,10 @@
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D89" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3717,10 +3726,10 @@
         <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D90" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3731,10 +3740,10 @@
         <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D91" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3745,10 +3754,10 @@
         <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D92" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3759,10 +3768,10 @@
         <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D93" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3773,10 +3782,10 @@
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D94" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3787,10 +3796,10 @@
         <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D95" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3801,10 +3810,10 @@
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D96" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3815,10 +3824,10 @@
         <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D97" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3829,10 +3838,10 @@
         <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D98" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3843,10 +3852,10 @@
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D99" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3854,10 +3863,10 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D100" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3868,10 +3877,10 @@
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D101" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3882,10 +3891,10 @@
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D102" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3896,10 +3905,10 @@
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D103" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3910,10 +3919,10 @@
         <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D104" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3921,10 +3930,10 @@
         <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D105" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3935,10 +3944,10 @@
         <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D106" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3946,10 +3955,10 @@
         <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D107" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3960,10 +3969,10 @@
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D108" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3974,10 +3983,10 @@
         <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D109" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3988,10 +3997,10 @@
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D110" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4002,10 +4011,10 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D111" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4016,10 +4025,10 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D112" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4027,10 +4036,10 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D113" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4038,10 +4047,10 @@
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D114" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4049,10 +4058,10 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D115" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4060,10 +4069,10 @@
         <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D116" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4074,10 +4083,10 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D117" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4088,10 +4097,10 @@
         <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D118" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4099,10 +4108,10 @@
         <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D119" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4110,10 +4119,10 @@
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D120" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4121,10 +4130,10 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D121" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4132,10 +4141,10 @@
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D122" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4143,10 +4152,10 @@
         <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D123" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4154,10 +4163,10 @@
         <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D124" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4168,10 +4177,10 @@
         <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D125" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4182,10 +4191,10 @@
         <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D126" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D127" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4210,10 +4219,10 @@
         <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D128" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4224,10 +4233,10 @@
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D129" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4238,10 +4247,10 @@
         <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D130" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4252,10 +4261,10 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D131" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4266,10 +4275,10 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D132" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4280,10 +4289,10 @@
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D133" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4294,10 +4303,10 @@
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D134" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4308,10 +4317,10 @@
         <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D135" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4322,10 +4331,10 @@
         <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D136" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4336,10 +4345,10 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D137" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4350,10 +4359,10 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D138" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4364,10 +4373,10 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D139" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4378,10 +4387,10 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D140" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4392,10 +4401,10 @@
         <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D141" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4406,10 +4415,10 @@
         <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D142" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4420,10 +4429,10 @@
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D143" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4434,10 +4443,10 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D144" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4448,10 +4457,10 @@
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D145" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4462,10 +4471,10 @@
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D146" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4476,10 +4485,10 @@
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D147" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4490,10 +4499,10 @@
         <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D148" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4504,10 +4513,10 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D149" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4518,10 +4527,10 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D150" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4532,10 +4541,10 @@
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D151" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4546,10 +4555,10 @@
         <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D152" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4560,10 +4569,10 @@
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D153" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4574,10 +4583,10 @@
         <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D154" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4588,10 +4597,10 @@
         <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D155" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4602,10 +4611,10 @@
         <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D156" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4616,10 +4625,10 @@
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D157" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D158" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D159" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4658,10 +4667,10 @@
         <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D160" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4672,10 +4681,10 @@
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D161" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4686,10 +4695,10 @@
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D162" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4700,10 +4709,10 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D163" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4714,10 +4723,10 @@
         <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D164" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4728,10 +4737,10 @@
         <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D165" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4742,10 +4751,10 @@
         <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D166" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4756,10 +4765,10 @@
         <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D167" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4770,10 +4779,10 @@
         <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D168" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4784,10 +4793,10 @@
         <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D169" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4798,10 +4807,10 @@
         <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D170" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D171" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4826,10 +4835,10 @@
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D172" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4840,10 +4849,10 @@
         <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D173" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4854,10 +4863,10 @@
         <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D174" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4868,10 +4877,10 @@
         <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D175" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4882,10 +4891,10 @@
         <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D176" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4896,10 +4905,10 @@
         <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D177" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4910,10 +4919,10 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D178" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4924,10 +4933,10 @@
         <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D179" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4938,10 +4947,10 @@
         <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D180" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4952,10 +4961,10 @@
         <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D181" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4966,10 +4975,10 @@
         <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D182" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4980,10 +4989,10 @@
         <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D183" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4994,10 +5003,10 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D184" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5008,10 +5017,10 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D185" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5022,10 +5031,10 @@
         <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D186" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D187" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5050,10 +5059,10 @@
         <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D188" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5064,10 +5073,10 @@
         <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D189" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5078,10 +5087,10 @@
         <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D190" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5092,10 +5101,10 @@
         <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D191" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5106,10 +5115,10 @@
         <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D192" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5120,10 +5129,10 @@
         <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D193" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5134,10 +5143,10 @@
         <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D194" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5148,10 +5157,10 @@
         <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D195" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5162,10 +5171,10 @@
         <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D196" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5176,10 +5185,10 @@
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D197" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5190,10 +5199,10 @@
         <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D198" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5204,10 +5213,10 @@
         <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D199" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5218,10 +5227,10 @@
         <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D200" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5232,10 +5241,10 @@
         <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D201" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5246,10 +5255,10 @@
         <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D202" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5260,10 +5269,10 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D203" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5274,10 +5283,10 @@
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D204" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5288,10 +5297,10 @@
         <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D205" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5302,10 +5311,10 @@
         <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D206" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5316,10 +5325,10 @@
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D207" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5330,10 +5339,10 @@
         <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D208" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5344,10 +5353,10 @@
         <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D209" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5358,10 +5367,10 @@
         <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D210" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5372,10 +5381,10 @@
         <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D211" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5386,10 +5395,10 @@
         <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D212" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5400,10 +5409,10 @@
         <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D213" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5414,10 +5423,10 @@
         <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D214" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5428,10 +5437,10 @@
         <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D215" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5442,10 +5451,10 @@
         <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D216" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5456,10 +5465,10 @@
         <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D217" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5470,10 +5479,10 @@
         <v>222</v>
       </c>
       <c r="C218" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D218" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5484,10 +5493,10 @@
         <v>223</v>
       </c>
       <c r="C219" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D219" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5498,10 +5507,10 @@
         <v>224</v>
       </c>
       <c r="C220" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D220" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5512,10 +5521,10 @@
         <v>225</v>
       </c>
       <c r="C221" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D221" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5526,10 +5535,10 @@
         <v>226</v>
       </c>
       <c r="C222" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D222" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5540,10 +5549,10 @@
         <v>227</v>
       </c>
       <c r="C223" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D223" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5554,10 +5563,10 @@
         <v>228</v>
       </c>
       <c r="C224" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D224" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5568,10 +5577,10 @@
         <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D225" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5582,10 +5591,10 @@
         <v>230</v>
       </c>
       <c r="C226" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D226" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5596,10 +5605,10 @@
         <v>231</v>
       </c>
       <c r="C227" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D227" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5610,10 +5619,10 @@
         <v>232</v>
       </c>
       <c r="C228" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D228" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5624,10 +5633,10 @@
         <v>233</v>
       </c>
       <c r="C229" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D229" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5638,10 +5647,10 @@
         <v>234</v>
       </c>
       <c r="C230" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D230" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5652,10 +5661,10 @@
         <v>235</v>
       </c>
       <c r="C231" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D231" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5666,10 +5675,10 @@
         <v>236</v>
       </c>
       <c r="C232" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D232" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5680,10 +5689,10 @@
         <v>237</v>
       </c>
       <c r="C233" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D233" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5694,7 +5703,7 @@
         <v>238</v>
       </c>
       <c r="C234" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D234" t="s">
         <v>238</v>
@@ -5708,10 +5717,24 @@
         <v>239</v>
       </c>
       <c r="C235" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D235" t="s">
         <v>239</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" t="s">
+        <v>4</v>
+      </c>
+      <c r="B236" t="s">
+        <v>240</v>
+      </c>
+      <c r="C236" t="s">
+        <v>475</v>
+      </c>
+      <c r="D236" t="s">
+        <v>708</v>
       </c>
     </row>
   </sheetData>

--- a/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
+++ b/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="712">
   <si>
     <t>THÔNG TIN KHO</t>
   </si>
@@ -739,6 +739,9 @@
     <t>B001</t>
   </si>
   <si>
+    <t>A266</t>
+  </si>
+  <si>
     <t>-4776256360</t>
   </si>
   <si>
@@ -1444,6 +1447,9 @@
     <t>-1004305022913</t>
   </si>
   <si>
+    <t>-1004376355185</t>
+  </si>
+  <si>
     <t>KFM_BDU_DAN - 27 Tân Lập</t>
   </si>
   <si>
@@ -2141,6 +2147,9 @@
   </si>
   <si>
     <t>KFM_HNI_YHO - CT3 Yên Hoà Park View</t>
+  </si>
+  <si>
+    <t>KFM_HCM_PNH - Hoa Sứ</t>
   </si>
 </sst>
 </file>
@@ -2472,7 +2481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D236"/>
+  <dimension ref="A1:D237"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2497,10 +2506,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2511,10 +2520,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2525,10 +2534,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D4" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2539,10 +2548,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D5" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2553,10 +2562,10 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D6" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2567,10 +2576,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D7" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2581,10 +2590,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D8" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2595,10 +2604,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D9" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2609,10 +2618,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D10" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2623,10 +2632,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D11" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2637,10 +2646,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D12" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2651,10 +2660,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D13" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2665,10 +2674,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D14" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2679,10 +2688,10 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D15" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2693,10 +2702,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D16" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2707,10 +2716,10 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D17" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2721,10 +2730,10 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D18" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2735,10 +2744,10 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D19" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2749,10 +2758,10 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D20" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2763,10 +2772,10 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D21" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2777,10 +2786,10 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2791,10 +2800,10 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D23" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2805,10 +2814,10 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2819,10 +2828,10 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D25" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2833,10 +2842,10 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2847,10 +2856,10 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D27" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2861,10 +2870,10 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D28" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2875,10 +2884,10 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D29" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2889,10 +2898,10 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D30" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2903,10 +2912,10 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D31" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2917,10 +2926,10 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D32" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2931,10 +2940,10 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D33" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2945,10 +2954,10 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D34" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2959,10 +2968,10 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D35" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2973,10 +2982,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D36" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2987,10 +2996,10 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D37" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3001,10 +3010,10 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D38" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3015,10 +3024,10 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D39" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3029,10 +3038,10 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D40" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3043,10 +3052,10 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D41" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3057,10 +3066,10 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D42" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3071,10 +3080,10 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D43" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3085,10 +3094,10 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D44" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3099,10 +3108,10 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D45" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3113,10 +3122,10 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D46" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3127,10 +3136,10 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D47" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3141,10 +3150,10 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D48" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3155,10 +3164,10 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D49" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3169,10 +3178,10 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D50" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3183,10 +3192,10 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D51" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3197,10 +3206,10 @@
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D52" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3211,10 +3220,10 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D53" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3225,10 +3234,10 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D54" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3239,10 +3248,10 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D55" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3253,10 +3262,10 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D56" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3267,10 +3276,10 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D57" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3281,10 +3290,10 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D58" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3295,10 +3304,10 @@
         <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D59" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3309,10 +3318,10 @@
         <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D60" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3323,10 +3332,10 @@
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D61" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3337,10 +3346,10 @@
         <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D62" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3351,10 +3360,10 @@
         <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D63" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3365,10 +3374,10 @@
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D64" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3379,10 +3388,10 @@
         <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D65" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3393,10 +3402,10 @@
         <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D66" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3407,10 +3416,10 @@
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D67" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3421,10 +3430,10 @@
         <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D68" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3435,10 +3444,10 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D69" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3449,10 +3458,10 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D70" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3463,10 +3472,10 @@
         <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D71" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3477,10 +3486,10 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D72" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3491,10 +3500,10 @@
         <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D73" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3505,10 +3514,10 @@
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D74" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3519,10 +3528,10 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D75" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3533,10 +3542,10 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D76" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3547,10 +3556,10 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D77" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3561,10 +3570,10 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D78" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3575,10 +3584,10 @@
         <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D79" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3589,10 +3598,10 @@
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D80" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3603,10 +3612,10 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D81" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3617,10 +3626,10 @@
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D82" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3631,10 +3640,10 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D83" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3645,10 +3654,10 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D84" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3659,10 +3668,10 @@
         <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D85" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3673,10 +3682,10 @@
         <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D86" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3687,10 +3696,10 @@
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D87" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3701,10 +3710,10 @@
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D88" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3715,10 +3724,10 @@
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D89" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3726,10 +3735,10 @@
         <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D90" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3740,10 +3749,10 @@
         <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D91" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3754,10 +3763,10 @@
         <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D92" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3768,10 +3777,10 @@
         <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D93" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3782,10 +3791,10 @@
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D94" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3796,10 +3805,10 @@
         <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D95" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3810,10 +3819,10 @@
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D96" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3824,10 +3833,10 @@
         <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D97" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3838,10 +3847,10 @@
         <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D98" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3852,10 +3861,10 @@
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D99" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3863,10 +3872,10 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D100" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3877,10 +3886,10 @@
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D101" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3891,10 +3900,10 @@
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D102" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3905,10 +3914,10 @@
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D103" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3919,10 +3928,10 @@
         <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D104" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3930,10 +3939,10 @@
         <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D105" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3944,10 +3953,10 @@
         <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D106" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3955,10 +3964,10 @@
         <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D107" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3969,10 +3978,10 @@
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D108" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3983,10 +3992,10 @@
         <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D109" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3997,10 +4006,10 @@
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D110" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4011,10 +4020,10 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D111" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4025,10 +4034,10 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D112" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4036,10 +4045,10 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D113" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4047,10 +4056,10 @@
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D114" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4058,10 +4067,10 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D115" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4069,10 +4078,10 @@
         <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D116" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4083,10 +4092,10 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D117" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4097,10 +4106,10 @@
         <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D118" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4108,10 +4117,10 @@
         <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D119" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4119,10 +4128,10 @@
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D120" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4130,10 +4139,10 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D121" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4141,10 +4150,10 @@
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D122" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4152,10 +4161,10 @@
         <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D123" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4163,10 +4172,10 @@
         <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D124" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4177,10 +4186,10 @@
         <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D125" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4191,10 +4200,10 @@
         <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D126" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4205,10 +4214,10 @@
         <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D127" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4219,10 +4228,10 @@
         <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D128" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4233,10 +4242,10 @@
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D129" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4247,10 +4256,10 @@
         <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D130" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4261,10 +4270,10 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D131" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4275,10 +4284,10 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D132" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4289,10 +4298,10 @@
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D133" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4303,10 +4312,10 @@
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D134" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4317,10 +4326,10 @@
         <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D135" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4331,10 +4340,10 @@
         <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D136" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4345,10 +4354,10 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D137" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4359,10 +4368,10 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D138" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4373,10 +4382,10 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D139" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4387,10 +4396,10 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D140" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4401,10 +4410,10 @@
         <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D141" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4415,10 +4424,10 @@
         <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D142" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4429,10 +4438,10 @@
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D143" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4443,10 +4452,10 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D144" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4457,10 +4466,10 @@
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D145" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4471,10 +4480,10 @@
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D146" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4485,10 +4494,10 @@
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D147" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4499,10 +4508,10 @@
         <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D148" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4513,10 +4522,10 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D149" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4527,10 +4536,10 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D150" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4541,10 +4550,10 @@
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D151" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4555,10 +4564,10 @@
         <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D152" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4569,10 +4578,10 @@
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D153" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4583,10 +4592,10 @@
         <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D154" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4597,10 +4606,10 @@
         <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D155" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4611,10 +4620,10 @@
         <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D156" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4625,10 +4634,10 @@
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D157" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4639,10 +4648,10 @@
         <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D158" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4653,10 +4662,10 @@
         <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D159" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4667,10 +4676,10 @@
         <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D160" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4681,10 +4690,10 @@
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D161" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4695,10 +4704,10 @@
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D162" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4709,10 +4718,10 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D163" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4723,10 +4732,10 @@
         <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D164" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4737,10 +4746,10 @@
         <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D165" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4751,10 +4760,10 @@
         <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D166" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4765,10 +4774,10 @@
         <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D167" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4779,10 +4788,10 @@
         <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D168" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4793,10 +4802,10 @@
         <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D169" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4807,10 +4816,10 @@
         <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D170" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4821,10 +4830,10 @@
         <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D171" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4835,10 +4844,10 @@
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D172" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4849,10 +4858,10 @@
         <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D173" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4863,10 +4872,10 @@
         <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D174" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4877,10 +4886,10 @@
         <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D175" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4891,10 +4900,10 @@
         <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D176" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4905,10 +4914,10 @@
         <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D177" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4919,10 +4928,10 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D178" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4933,10 +4942,10 @@
         <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D179" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4947,10 +4956,10 @@
         <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D180" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4961,10 +4970,10 @@
         <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D181" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4975,10 +4984,10 @@
         <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D182" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4989,10 +4998,10 @@
         <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D183" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5003,10 +5012,10 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D184" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5017,10 +5026,10 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D185" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5031,10 +5040,10 @@
         <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D186" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5045,10 +5054,10 @@
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D187" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5059,10 +5068,10 @@
         <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D188" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5073,10 +5082,10 @@
         <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D189" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5087,10 +5096,10 @@
         <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D190" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5101,10 +5110,10 @@
         <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D191" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5115,10 +5124,10 @@
         <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D192" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5129,10 +5138,10 @@
         <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D193" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5143,10 +5152,10 @@
         <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D194" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5157,10 +5166,10 @@
         <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D195" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5171,10 +5180,10 @@
         <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D196" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5185,10 +5194,10 @@
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D197" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5199,10 +5208,10 @@
         <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D198" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5213,10 +5222,10 @@
         <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D199" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5227,10 +5236,10 @@
         <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D200" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5241,10 +5250,10 @@
         <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D201" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5255,10 +5264,10 @@
         <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D202" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5269,10 +5278,10 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D203" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5283,10 +5292,10 @@
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D204" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5297,10 +5306,10 @@
         <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D205" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5311,10 +5320,10 @@
         <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D206" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5325,10 +5334,10 @@
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D207" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5339,10 +5348,10 @@
         <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D208" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5353,10 +5362,10 @@
         <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D209" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5367,10 +5376,10 @@
         <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D210" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5381,10 +5390,10 @@
         <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D211" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5395,10 +5404,10 @@
         <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D212" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5409,10 +5418,10 @@
         <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D213" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5423,10 +5432,10 @@
         <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D214" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5437,10 +5446,10 @@
         <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D215" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5451,10 +5460,10 @@
         <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D216" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5465,10 +5474,10 @@
         <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D217" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5479,10 +5488,10 @@
         <v>222</v>
       </c>
       <c r="C218" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D218" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5493,10 +5502,10 @@
         <v>223</v>
       </c>
       <c r="C219" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D219" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5507,10 +5516,10 @@
         <v>224</v>
       </c>
       <c r="C220" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D220" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5521,10 +5530,10 @@
         <v>225</v>
       </c>
       <c r="C221" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D221" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5535,10 +5544,10 @@
         <v>226</v>
       </c>
       <c r="C222" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D222" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5549,10 +5558,10 @@
         <v>227</v>
       </c>
       <c r="C223" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D223" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5563,10 +5572,10 @@
         <v>228</v>
       </c>
       <c r="C224" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D224" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5577,10 +5586,10 @@
         <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D225" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5591,10 +5600,10 @@
         <v>230</v>
       </c>
       <c r="C226" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D226" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5605,10 +5614,10 @@
         <v>231</v>
       </c>
       <c r="C227" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D227" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5619,10 +5628,10 @@
         <v>232</v>
       </c>
       <c r="C228" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D228" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5633,10 +5642,10 @@
         <v>233</v>
       </c>
       <c r="C229" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D229" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5647,10 +5656,10 @@
         <v>234</v>
       </c>
       <c r="C230" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D230" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5661,10 +5670,10 @@
         <v>235</v>
       </c>
       <c r="C231" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D231" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5675,10 +5684,10 @@
         <v>236</v>
       </c>
       <c r="C232" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D232" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5689,10 +5698,10 @@
         <v>237</v>
       </c>
       <c r="C233" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D233" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5703,7 +5712,7 @@
         <v>238</v>
       </c>
       <c r="C234" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D234" t="s">
         <v>238</v>
@@ -5717,7 +5726,7 @@
         <v>239</v>
       </c>
       <c r="C235" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D235" t="s">
         <v>239</v>
@@ -5731,10 +5740,24 @@
         <v>240</v>
       </c>
       <c r="C236" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D236" t="s">
-        <v>708</v>
+        <v>710</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" t="s">
+        <v>4</v>
+      </c>
+      <c r="B237" t="s">
+        <v>241</v>
+      </c>
+      <c r="C237" t="s">
+        <v>477</v>
+      </c>
+      <c r="D237" t="s">
+        <v>711</v>
       </c>
     </row>
   </sheetData>

--- a/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
+++ b/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="715">
   <si>
     <t>THÔNG TIN KHO</t>
   </si>
@@ -742,6 +742,9 @@
     <t>A266</t>
   </si>
   <si>
+    <t>A254</t>
+  </si>
+  <si>
     <t>-4776256360</t>
   </si>
   <si>
@@ -1450,6 +1453,9 @@
     <t>-1004376355185</t>
   </si>
   <si>
+    <t>-1003932058795</t>
+  </si>
+  <si>
     <t>KFM_BDU_DAN - 27 Tân Lập</t>
   </si>
   <si>
@@ -2150,6 +2156,9 @@
   </si>
   <si>
     <t>KFM_HCM_PNH - Hoa Sứ</t>
+  </si>
+  <si>
+    <t>KFM_HCM_Q12 - S.06 Chung Cư Phú Cường Home</t>
   </si>
 </sst>
 </file>
@@ -2481,7 +2490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D237"/>
+  <dimension ref="A1:D238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2506,10 +2515,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2520,10 +2529,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2534,10 +2543,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D4" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2548,10 +2557,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D5" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2562,10 +2571,10 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D6" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2576,10 +2585,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D7" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2590,10 +2599,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D8" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2604,10 +2613,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D9" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2618,10 +2627,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2632,10 +2641,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D11" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2646,10 +2655,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D12" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2660,10 +2669,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D13" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2674,10 +2683,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D14" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2688,10 +2697,10 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D15" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2702,10 +2711,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D16" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2716,10 +2725,10 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D17" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2730,10 +2739,10 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2744,10 +2753,10 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D19" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2758,10 +2767,10 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D20" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2772,10 +2781,10 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2786,10 +2795,10 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D22" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2800,10 +2809,10 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D23" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2814,10 +2823,10 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2828,10 +2837,10 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2842,10 +2851,10 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D26" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2856,10 +2865,10 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D27" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2870,10 +2879,10 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D28" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2884,10 +2893,10 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D29" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2898,10 +2907,10 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D30" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2912,10 +2921,10 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2926,10 +2935,10 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D32" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2940,10 +2949,10 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D33" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2954,10 +2963,10 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D34" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2968,10 +2977,10 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D35" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2982,10 +2991,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D36" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2996,10 +3005,10 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D37" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3010,10 +3019,10 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D38" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3024,10 +3033,10 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D39" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3038,10 +3047,10 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D40" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3052,10 +3061,10 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D41" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3066,10 +3075,10 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D42" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3080,10 +3089,10 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D43" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3094,10 +3103,10 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D44" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3108,10 +3117,10 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D45" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3122,10 +3131,10 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D46" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3136,10 +3145,10 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D47" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3150,10 +3159,10 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D48" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3164,10 +3173,10 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D49" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3178,10 +3187,10 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D50" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3192,10 +3201,10 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D51" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3206,10 +3215,10 @@
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D52" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3220,10 +3229,10 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D53" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3234,10 +3243,10 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D54" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3248,10 +3257,10 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D55" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3262,10 +3271,10 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D56" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3276,10 +3285,10 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D57" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3290,10 +3299,10 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D58" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3304,10 +3313,10 @@
         <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D59" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3318,10 +3327,10 @@
         <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D60" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3332,10 +3341,10 @@
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D61" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3346,10 +3355,10 @@
         <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D62" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3360,10 +3369,10 @@
         <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D63" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3374,10 +3383,10 @@
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D64" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3388,10 +3397,10 @@
         <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D65" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3402,10 +3411,10 @@
         <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D66" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3416,10 +3425,10 @@
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D67" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3430,10 +3439,10 @@
         <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D68" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3444,10 +3453,10 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D69" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3458,10 +3467,10 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D70" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3472,10 +3481,10 @@
         <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D71" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3486,10 +3495,10 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D72" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3500,10 +3509,10 @@
         <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D73" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3514,10 +3523,10 @@
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D74" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3528,10 +3537,10 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D75" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3542,10 +3551,10 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D76" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3556,10 +3565,10 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D77" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3570,10 +3579,10 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D78" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3584,10 +3593,10 @@
         <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D79" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3598,10 +3607,10 @@
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D80" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3612,10 +3621,10 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D81" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3626,10 +3635,10 @@
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D82" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3640,10 +3649,10 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D83" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3654,10 +3663,10 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D84" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3668,10 +3677,10 @@
         <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D85" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3682,10 +3691,10 @@
         <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D86" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3696,10 +3705,10 @@
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D87" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3710,10 +3719,10 @@
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D88" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3724,10 +3733,10 @@
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D89" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3735,10 +3744,10 @@
         <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D90" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3749,10 +3758,10 @@
         <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D91" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3763,10 +3772,10 @@
         <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D92" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3777,10 +3786,10 @@
         <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D93" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3791,10 +3800,10 @@
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D94" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3805,10 +3814,10 @@
         <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D95" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3819,10 +3828,10 @@
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D96" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3833,10 +3842,10 @@
         <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D97" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3847,10 +3856,10 @@
         <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D98" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3861,10 +3870,10 @@
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D99" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3872,10 +3881,10 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D100" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3886,10 +3895,10 @@
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D101" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3900,10 +3909,10 @@
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D102" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3914,10 +3923,10 @@
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D103" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3928,10 +3937,10 @@
         <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D104" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3939,10 +3948,10 @@
         <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D105" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3953,10 +3962,10 @@
         <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D106" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3964,10 +3973,10 @@
         <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D107" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3978,10 +3987,10 @@
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D108" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3992,10 +4001,10 @@
         <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D109" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -4006,10 +4015,10 @@
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D110" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4020,10 +4029,10 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D111" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4034,10 +4043,10 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D112" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4045,10 +4054,10 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D113" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4056,10 +4065,10 @@
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D114" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4067,10 +4076,10 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D115" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4078,10 +4087,10 @@
         <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D116" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4092,10 +4101,10 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D117" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4106,10 +4115,10 @@
         <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D118" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4117,10 +4126,10 @@
         <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D119" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4128,10 +4137,10 @@
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D120" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4139,10 +4148,10 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D121" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4150,10 +4159,10 @@
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D122" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4161,10 +4170,10 @@
         <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D123" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4172,10 +4181,10 @@
         <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D124" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4186,10 +4195,10 @@
         <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D125" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4200,10 +4209,10 @@
         <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D126" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4214,10 +4223,10 @@
         <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D127" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4228,10 +4237,10 @@
         <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D128" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4242,10 +4251,10 @@
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D129" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4256,10 +4265,10 @@
         <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D130" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4270,10 +4279,10 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D131" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4284,10 +4293,10 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D132" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4298,10 +4307,10 @@
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D133" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4312,10 +4321,10 @@
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D134" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4326,10 +4335,10 @@
         <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D135" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4340,10 +4349,10 @@
         <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D136" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4354,10 +4363,10 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D137" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4368,10 +4377,10 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D138" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4382,10 +4391,10 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D139" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4396,10 +4405,10 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D140" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4410,10 +4419,10 @@
         <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D141" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4424,10 +4433,10 @@
         <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D142" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4438,10 +4447,10 @@
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D143" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4452,10 +4461,10 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D144" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4466,10 +4475,10 @@
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D145" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4480,10 +4489,10 @@
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D146" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4494,10 +4503,10 @@
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D147" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4508,10 +4517,10 @@
         <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D148" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4522,10 +4531,10 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D149" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4536,10 +4545,10 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D150" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4550,10 +4559,10 @@
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D151" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4564,10 +4573,10 @@
         <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D152" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4578,10 +4587,10 @@
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D153" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4592,10 +4601,10 @@
         <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D154" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4606,10 +4615,10 @@
         <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D155" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4620,10 +4629,10 @@
         <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D156" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4634,10 +4643,10 @@
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D157" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4648,10 +4657,10 @@
         <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D158" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4662,10 +4671,10 @@
         <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D159" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4676,10 +4685,10 @@
         <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D160" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4690,10 +4699,10 @@
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D161" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4704,10 +4713,10 @@
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D162" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4718,10 +4727,10 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D163" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4732,10 +4741,10 @@
         <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D164" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4746,10 +4755,10 @@
         <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D165" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4760,10 +4769,10 @@
         <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D166" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4774,10 +4783,10 @@
         <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D167" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4788,10 +4797,10 @@
         <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D168" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4802,10 +4811,10 @@
         <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D169" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4816,10 +4825,10 @@
         <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D170" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4830,10 +4839,10 @@
         <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D171" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4844,10 +4853,10 @@
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D172" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4858,10 +4867,10 @@
         <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D173" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4872,10 +4881,10 @@
         <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D174" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4886,10 +4895,10 @@
         <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D175" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4900,10 +4909,10 @@
         <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D176" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4914,10 +4923,10 @@
         <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D177" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4928,10 +4937,10 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D178" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4942,10 +4951,10 @@
         <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D179" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4956,10 +4965,10 @@
         <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D180" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4970,10 +4979,10 @@
         <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D181" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4984,10 +4993,10 @@
         <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D182" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4998,10 +5007,10 @@
         <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D183" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5012,10 +5021,10 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D184" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5026,10 +5035,10 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D185" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5040,10 +5049,10 @@
         <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D186" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5054,10 +5063,10 @@
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D187" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5068,10 +5077,10 @@
         <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D188" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5082,10 +5091,10 @@
         <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D189" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5096,10 +5105,10 @@
         <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D190" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5110,10 +5119,10 @@
         <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D191" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5124,10 +5133,10 @@
         <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D192" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5138,10 +5147,10 @@
         <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D193" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5152,10 +5161,10 @@
         <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D194" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5166,10 +5175,10 @@
         <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D195" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5180,10 +5189,10 @@
         <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D196" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5194,10 +5203,10 @@
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D197" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5208,10 +5217,10 @@
         <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D198" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5222,10 +5231,10 @@
         <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D199" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5236,10 +5245,10 @@
         <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D200" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5250,10 +5259,10 @@
         <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D201" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5264,10 +5273,10 @@
         <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D202" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5278,10 +5287,10 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D203" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5292,10 +5301,10 @@
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D204" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5306,10 +5315,10 @@
         <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D205" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5320,10 +5329,10 @@
         <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D206" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5334,10 +5343,10 @@
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D207" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5348,10 +5357,10 @@
         <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D208" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5362,10 +5371,10 @@
         <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D209" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5376,10 +5385,10 @@
         <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D210" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5390,10 +5399,10 @@
         <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D211" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5404,10 +5413,10 @@
         <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D212" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5418,10 +5427,10 @@
         <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D213" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5432,10 +5441,10 @@
         <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D214" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5446,10 +5455,10 @@
         <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D215" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5460,10 +5469,10 @@
         <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D216" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5474,10 +5483,10 @@
         <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D217" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5488,10 +5497,10 @@
         <v>222</v>
       </c>
       <c r="C218" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D218" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5502,10 +5511,10 @@
         <v>223</v>
       </c>
       <c r="C219" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D219" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5516,10 +5525,10 @@
         <v>224</v>
       </c>
       <c r="C220" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D220" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5530,10 +5539,10 @@
         <v>225</v>
       </c>
       <c r="C221" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D221" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5544,10 +5553,10 @@
         <v>226</v>
       </c>
       <c r="C222" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D222" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5558,10 +5567,10 @@
         <v>227</v>
       </c>
       <c r="C223" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D223" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5572,10 +5581,10 @@
         <v>228</v>
       </c>
       <c r="C224" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D224" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5586,10 +5595,10 @@
         <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D225" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5600,10 +5609,10 @@
         <v>230</v>
       </c>
       <c r="C226" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D226" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5614,10 +5623,10 @@
         <v>231</v>
       </c>
       <c r="C227" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D227" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5628,10 +5637,10 @@
         <v>232</v>
       </c>
       <c r="C228" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D228" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5642,10 +5651,10 @@
         <v>233</v>
       </c>
       <c r="C229" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D229" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5656,10 +5665,10 @@
         <v>234</v>
       </c>
       <c r="C230" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D230" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5670,10 +5679,10 @@
         <v>235</v>
       </c>
       <c r="C231" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D231" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5684,10 +5693,10 @@
         <v>236</v>
       </c>
       <c r="C232" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D232" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5698,10 +5707,10 @@
         <v>237</v>
       </c>
       <c r="C233" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D233" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5712,7 +5721,7 @@
         <v>238</v>
       </c>
       <c r="C234" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D234" t="s">
         <v>238</v>
@@ -5726,7 +5735,7 @@
         <v>239</v>
       </c>
       <c r="C235" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D235" t="s">
         <v>239</v>
@@ -5740,10 +5749,10 @@
         <v>240</v>
       </c>
       <c r="C236" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D236" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5754,10 +5763,24 @@
         <v>241</v>
       </c>
       <c r="C237" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D237" t="s">
-        <v>711</v>
+        <v>713</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" t="s">
+        <v>4</v>
+      </c>
+      <c r="B238" t="s">
+        <v>242</v>
+      </c>
+      <c r="C238" t="s">
+        <v>479</v>
+      </c>
+      <c r="D238" t="s">
+        <v>714</v>
       </c>
     </row>
   </sheetData>

--- a/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
+++ b/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="718">
   <si>
     <t>THÔNG TIN KHO</t>
   </si>
@@ -745,6 +745,9 @@
     <t>A254</t>
   </si>
   <si>
+    <t>A262</t>
+  </si>
+  <si>
     <t>-4776256360</t>
   </si>
   <si>
@@ -1456,6 +1459,9 @@
     <t>-1003932058795</t>
   </si>
   <si>
+    <t>-1004438420846</t>
+  </si>
+  <si>
     <t>KFM_BDU_DAN - 27 Tân Lập</t>
   </si>
   <si>
@@ -2159,6 +2165,9 @@
   </si>
   <si>
     <t>KFM_HCM_Q12 - S.06 Chung Cư Phú Cường Home</t>
+  </si>
+  <si>
+    <t>KFM_BDU_DAN - R01.14 Block A2 Charm Ruby</t>
   </si>
 </sst>
 </file>
@@ -2490,7 +2499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D238"/>
+  <dimension ref="A1:D239"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2515,10 +2524,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2529,10 +2538,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2543,10 +2552,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D4" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2557,10 +2566,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D5" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2571,10 +2580,10 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D6" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2585,10 +2594,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D7" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2599,10 +2608,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D8" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2613,10 +2622,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D9" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2627,10 +2636,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D10" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2641,10 +2650,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2655,10 +2664,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D12" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2669,10 +2678,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D13" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2683,10 +2692,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D14" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2697,10 +2706,10 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D15" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2711,10 +2720,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D16" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2725,10 +2734,10 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D17" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2739,10 +2748,10 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D18" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2753,10 +2762,10 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D19" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2767,10 +2776,10 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2781,10 +2790,10 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D21" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2795,10 +2804,10 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D22" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2809,10 +2818,10 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D23" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2823,10 +2832,10 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2837,10 +2846,10 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D25" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2851,10 +2860,10 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D26" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2865,10 +2874,10 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D27" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2879,10 +2888,10 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D28" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2893,10 +2902,10 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D29" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2907,10 +2916,10 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D30" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2921,10 +2930,10 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2935,10 +2944,10 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D32" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2949,10 +2958,10 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D33" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2963,10 +2972,10 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D34" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2977,10 +2986,10 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D35" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2991,10 +3000,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D36" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3005,10 +3014,10 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D37" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3019,10 +3028,10 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D38" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3033,10 +3042,10 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D39" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3047,10 +3056,10 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D40" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3061,10 +3070,10 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D41" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3075,10 +3084,10 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D42" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3089,10 +3098,10 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D43" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3103,10 +3112,10 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D44" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3117,10 +3126,10 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D45" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3131,10 +3140,10 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D46" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3145,10 +3154,10 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D47" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3159,10 +3168,10 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D48" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3173,10 +3182,10 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D49" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3187,10 +3196,10 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D50" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3201,10 +3210,10 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D51" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3215,10 +3224,10 @@
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D52" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3229,10 +3238,10 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D53" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3243,10 +3252,10 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D54" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3257,10 +3266,10 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D55" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3271,10 +3280,10 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D56" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3285,10 +3294,10 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D57" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3299,10 +3308,10 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D58" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3313,10 +3322,10 @@
         <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D59" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3327,10 +3336,10 @@
         <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D60" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3341,10 +3350,10 @@
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D61" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3355,10 +3364,10 @@
         <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D62" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3369,10 +3378,10 @@
         <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D63" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3383,10 +3392,10 @@
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D64" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3397,10 +3406,10 @@
         <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D65" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3411,10 +3420,10 @@
         <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D66" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3425,10 +3434,10 @@
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D67" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3439,10 +3448,10 @@
         <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D68" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3453,10 +3462,10 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D69" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3467,10 +3476,10 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D70" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3481,10 +3490,10 @@
         <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D71" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3495,10 +3504,10 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D72" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3509,10 +3518,10 @@
         <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D73" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3523,10 +3532,10 @@
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D74" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3537,10 +3546,10 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D75" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3551,10 +3560,10 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D76" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3565,10 +3574,10 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D77" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3579,10 +3588,10 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D78" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3593,10 +3602,10 @@
         <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D79" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3607,10 +3616,10 @@
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D80" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3621,10 +3630,10 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D81" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3635,10 +3644,10 @@
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D82" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3649,10 +3658,10 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D83" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3663,10 +3672,10 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D84" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3677,10 +3686,10 @@
         <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D85" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3691,10 +3700,10 @@
         <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D86" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3705,10 +3714,10 @@
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D87" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3719,10 +3728,10 @@
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D88" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3733,10 +3742,10 @@
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D89" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3744,10 +3753,10 @@
         <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D90" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3758,10 +3767,10 @@
         <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D91" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3772,10 +3781,10 @@
         <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D92" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3786,10 +3795,10 @@
         <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D93" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3800,10 +3809,10 @@
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D94" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3814,10 +3823,10 @@
         <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D95" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3828,10 +3837,10 @@
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D96" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3842,10 +3851,10 @@
         <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D97" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3856,10 +3865,10 @@
         <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D98" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3870,10 +3879,10 @@
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D99" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3881,10 +3890,10 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D100" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3895,10 +3904,10 @@
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D101" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3909,10 +3918,10 @@
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D102" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3923,10 +3932,10 @@
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D103" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3937,10 +3946,10 @@
         <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D104" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3948,10 +3957,10 @@
         <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D105" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3962,10 +3971,10 @@
         <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D106" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3973,10 +3982,10 @@
         <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D107" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3987,10 +3996,10 @@
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D108" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -4001,10 +4010,10 @@
         <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D109" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -4015,10 +4024,10 @@
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D110" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4029,10 +4038,10 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D111" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4043,10 +4052,10 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D112" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4054,10 +4063,10 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D113" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4065,10 +4074,10 @@
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D114" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4076,10 +4085,10 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D115" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4087,10 +4096,10 @@
         <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D116" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4101,10 +4110,10 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D117" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4115,10 +4124,10 @@
         <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D118" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4126,10 +4135,10 @@
         <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D119" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4137,10 +4146,10 @@
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D120" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4148,10 +4157,10 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D121" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4159,10 +4168,10 @@
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D122" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4170,10 +4179,10 @@
         <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D123" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4181,10 +4190,10 @@
         <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D124" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4195,10 +4204,10 @@
         <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D125" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4209,10 +4218,10 @@
         <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D126" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4223,10 +4232,10 @@
         <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D127" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4237,10 +4246,10 @@
         <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D128" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4251,10 +4260,10 @@
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D129" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4265,10 +4274,10 @@
         <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D130" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4279,10 +4288,10 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D131" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4293,10 +4302,10 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D132" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4307,10 +4316,10 @@
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D133" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4321,10 +4330,10 @@
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D134" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4335,10 +4344,10 @@
         <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D135" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4349,10 +4358,10 @@
         <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D136" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4363,10 +4372,10 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D137" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4377,10 +4386,10 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D138" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4391,10 +4400,10 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D139" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4405,10 +4414,10 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D140" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4419,10 +4428,10 @@
         <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D141" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4433,10 +4442,10 @@
         <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D142" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4447,10 +4456,10 @@
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D143" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4461,10 +4470,10 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D144" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4475,10 +4484,10 @@
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D145" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4489,10 +4498,10 @@
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D146" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4503,10 +4512,10 @@
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D147" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4517,10 +4526,10 @@
         <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D148" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4531,10 +4540,10 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D149" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4545,10 +4554,10 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D150" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4559,10 +4568,10 @@
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D151" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4573,10 +4582,10 @@
         <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D152" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4587,10 +4596,10 @@
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D153" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4601,10 +4610,10 @@
         <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D154" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4615,10 +4624,10 @@
         <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D155" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4629,10 +4638,10 @@
         <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D156" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4643,10 +4652,10 @@
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D157" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4657,10 +4666,10 @@
         <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D158" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4671,10 +4680,10 @@
         <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D159" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4685,10 +4694,10 @@
         <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D160" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4699,10 +4708,10 @@
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D161" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4713,10 +4722,10 @@
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D162" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4727,10 +4736,10 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D163" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4741,10 +4750,10 @@
         <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D164" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4755,10 +4764,10 @@
         <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D165" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4769,10 +4778,10 @@
         <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D166" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4783,10 +4792,10 @@
         <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D167" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4797,10 +4806,10 @@
         <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D168" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4811,10 +4820,10 @@
         <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D169" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4825,10 +4834,10 @@
         <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D170" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4839,10 +4848,10 @@
         <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D171" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4853,10 +4862,10 @@
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D172" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4867,10 +4876,10 @@
         <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D173" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4881,10 +4890,10 @@
         <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D174" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4895,10 +4904,10 @@
         <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D175" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4909,10 +4918,10 @@
         <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D176" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4923,10 +4932,10 @@
         <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D177" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4937,10 +4946,10 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D178" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4951,10 +4960,10 @@
         <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D179" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4965,10 +4974,10 @@
         <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D180" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4979,10 +4988,10 @@
         <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D181" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4993,10 +5002,10 @@
         <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D182" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5007,10 +5016,10 @@
         <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D183" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5021,10 +5030,10 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D184" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5035,10 +5044,10 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D185" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5049,10 +5058,10 @@
         <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D186" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5063,10 +5072,10 @@
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D187" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5077,10 +5086,10 @@
         <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D188" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5091,10 +5100,10 @@
         <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D189" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5105,10 +5114,10 @@
         <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D190" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5119,10 +5128,10 @@
         <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D191" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5133,10 +5142,10 @@
         <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D192" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5147,10 +5156,10 @@
         <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D193" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5161,10 +5170,10 @@
         <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D194" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5175,10 +5184,10 @@
         <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D195" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5189,10 +5198,10 @@
         <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D196" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5203,10 +5212,10 @@
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D197" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5217,10 +5226,10 @@
         <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D198" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5231,10 +5240,10 @@
         <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D199" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5245,10 +5254,10 @@
         <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D200" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5259,10 +5268,10 @@
         <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D201" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5273,10 +5282,10 @@
         <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D202" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5287,10 +5296,10 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D203" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5301,10 +5310,10 @@
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D204" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5315,10 +5324,10 @@
         <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D205" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5329,10 +5338,10 @@
         <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D206" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5343,10 +5352,10 @@
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D207" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5357,10 +5366,10 @@
         <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D208" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5371,10 +5380,10 @@
         <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D209" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5385,10 +5394,10 @@
         <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D210" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5399,10 +5408,10 @@
         <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D211" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5413,10 +5422,10 @@
         <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D212" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5427,10 +5436,10 @@
         <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D213" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5441,10 +5450,10 @@
         <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D214" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5455,10 +5464,10 @@
         <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D215" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5469,10 +5478,10 @@
         <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D216" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5483,10 +5492,10 @@
         <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D217" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5497,10 +5506,10 @@
         <v>222</v>
       </c>
       <c r="C218" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D218" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5511,10 +5520,10 @@
         <v>223</v>
       </c>
       <c r="C219" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D219" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5525,10 +5534,10 @@
         <v>224</v>
       </c>
       <c r="C220" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D220" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5539,10 +5548,10 @@
         <v>225</v>
       </c>
       <c r="C221" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D221" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5553,10 +5562,10 @@
         <v>226</v>
       </c>
       <c r="C222" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D222" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5567,10 +5576,10 @@
         <v>227</v>
       </c>
       <c r="C223" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D223" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5581,10 +5590,10 @@
         <v>228</v>
       </c>
       <c r="C224" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D224" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5595,10 +5604,10 @@
         <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D225" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5609,10 +5618,10 @@
         <v>230</v>
       </c>
       <c r="C226" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D226" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5623,10 +5632,10 @@
         <v>231</v>
       </c>
       <c r="C227" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D227" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5637,10 +5646,10 @@
         <v>232</v>
       </c>
       <c r="C228" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D228" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5651,10 +5660,10 @@
         <v>233</v>
       </c>
       <c r="C229" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D229" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5665,10 +5674,10 @@
         <v>234</v>
       </c>
       <c r="C230" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D230" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5679,10 +5688,10 @@
         <v>235</v>
       </c>
       <c r="C231" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D231" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5693,10 +5702,10 @@
         <v>236</v>
       </c>
       <c r="C232" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D232" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5707,10 +5716,10 @@
         <v>237</v>
       </c>
       <c r="C233" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D233" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5721,7 +5730,7 @@
         <v>238</v>
       </c>
       <c r="C234" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D234" t="s">
         <v>238</v>
@@ -5735,7 +5744,7 @@
         <v>239</v>
       </c>
       <c r="C235" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D235" t="s">
         <v>239</v>
@@ -5749,10 +5758,10 @@
         <v>240</v>
       </c>
       <c r="C236" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D236" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5763,10 +5772,10 @@
         <v>241</v>
       </c>
       <c r="C237" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D237" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5777,10 +5786,24 @@
         <v>242</v>
       </c>
       <c r="C238" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D238" t="s">
-        <v>714</v>
+        <v>716</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" t="s">
+        <v>4</v>
+      </c>
+      <c r="B239" t="s">
+        <v>243</v>
+      </c>
+      <c r="C239" t="s">
+        <v>481</v>
+      </c>
+      <c r="D239" t="s">
+        <v>717</v>
       </c>
     </row>
   </sheetData>

--- a/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
+++ b/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="721">
   <si>
     <t>THÔNG TIN KHO</t>
   </si>
@@ -748,6 +748,9 @@
     <t>A262</t>
   </si>
   <si>
+    <t>A243</t>
+  </si>
+  <si>
     <t>-4776256360</t>
   </si>
   <si>
@@ -1462,6 +1465,9 @@
     <t>-1004438420846</t>
   </si>
   <si>
+    <t>-1003932619661</t>
+  </si>
+  <si>
     <t>KFM_BDU_DAN - 27 Tân Lập</t>
   </si>
   <si>
@@ -2168,6 +2174,9 @@
   </si>
   <si>
     <t>KFM_BDU_DAN - R01.14 Block A2 Charm Ruby</t>
+  </si>
+  <si>
+    <t>KFM_HCM_Q08 - A6-7 Block A Diamond Lotus Riverside</t>
   </si>
 </sst>
 </file>
@@ -2499,7 +2508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D239"/>
+  <dimension ref="A1:D240"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2524,10 +2533,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2538,10 +2547,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2552,10 +2561,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D4" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2566,10 +2575,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D5" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2580,10 +2589,10 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D6" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2594,10 +2603,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D7" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2608,10 +2617,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2622,10 +2631,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D9" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2636,10 +2645,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D10" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2650,10 +2659,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D11" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2664,10 +2673,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D12" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2678,10 +2687,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D13" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2692,10 +2701,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D14" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2706,10 +2715,10 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D15" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2720,10 +2729,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2734,10 +2743,10 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D17" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2748,10 +2757,10 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2762,10 +2771,10 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2776,10 +2785,10 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D20" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2790,10 +2799,10 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2804,10 +2813,10 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D22" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2818,10 +2827,10 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D23" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2832,10 +2841,10 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D24" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2846,10 +2855,10 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D25" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2860,10 +2869,10 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D26" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2874,10 +2883,10 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D27" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2888,10 +2897,10 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D28" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2902,10 +2911,10 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D29" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2916,10 +2925,10 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D30" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2930,10 +2939,10 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2944,10 +2953,10 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D32" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2958,10 +2967,10 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D33" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2972,10 +2981,10 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D34" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2986,10 +2995,10 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D35" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3000,10 +3009,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D36" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3014,10 +3023,10 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D37" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3028,10 +3037,10 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D38" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3042,10 +3051,10 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D39" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3056,10 +3065,10 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D40" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3070,10 +3079,10 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D41" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3084,10 +3093,10 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D42" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3098,10 +3107,10 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D43" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3112,10 +3121,10 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D44" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3126,10 +3135,10 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D45" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3140,10 +3149,10 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D46" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3154,10 +3163,10 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D47" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3168,10 +3177,10 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D48" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3182,10 +3191,10 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D49" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3196,10 +3205,10 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D50" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3210,10 +3219,10 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D51" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3224,10 +3233,10 @@
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D52" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3238,10 +3247,10 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D53" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3252,10 +3261,10 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D54" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3266,10 +3275,10 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D55" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3280,10 +3289,10 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D56" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3294,10 +3303,10 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D57" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3308,10 +3317,10 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D58" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3322,10 +3331,10 @@
         <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D59" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3336,10 +3345,10 @@
         <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D60" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3350,10 +3359,10 @@
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D61" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3364,10 +3373,10 @@
         <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D62" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3378,10 +3387,10 @@
         <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D63" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3392,10 +3401,10 @@
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D64" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3406,10 +3415,10 @@
         <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D65" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3420,10 +3429,10 @@
         <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D66" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3434,10 +3443,10 @@
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D67" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3448,10 +3457,10 @@
         <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D68" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3462,10 +3471,10 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D69" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3476,10 +3485,10 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D70" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3490,10 +3499,10 @@
         <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D71" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3504,10 +3513,10 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D72" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3518,10 +3527,10 @@
         <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D73" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3532,10 +3541,10 @@
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D74" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3546,10 +3555,10 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D75" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3560,10 +3569,10 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D76" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3574,10 +3583,10 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D77" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3588,10 +3597,10 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D78" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3602,10 +3611,10 @@
         <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D79" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3616,10 +3625,10 @@
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D80" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3630,10 +3639,10 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D81" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3644,10 +3653,10 @@
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D82" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3658,10 +3667,10 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D83" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3672,10 +3681,10 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D84" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3686,10 +3695,10 @@
         <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D85" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3700,10 +3709,10 @@
         <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D86" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3714,10 +3723,10 @@
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D87" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3728,10 +3737,10 @@
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D88" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3742,10 +3751,10 @@
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D89" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3753,10 +3762,10 @@
         <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D90" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3767,10 +3776,10 @@
         <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D91" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3781,10 +3790,10 @@
         <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D92" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3795,10 +3804,10 @@
         <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D93" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3809,10 +3818,10 @@
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D94" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3823,10 +3832,10 @@
         <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D95" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3837,10 +3846,10 @@
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D96" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3851,10 +3860,10 @@
         <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D97" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3865,10 +3874,10 @@
         <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D98" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3879,10 +3888,10 @@
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D99" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3890,10 +3899,10 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D100" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3904,10 +3913,10 @@
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D101" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3918,10 +3927,10 @@
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D102" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3932,10 +3941,10 @@
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D103" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3946,10 +3955,10 @@
         <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D104" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3957,10 +3966,10 @@
         <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D105" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3971,10 +3980,10 @@
         <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D106" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3982,10 +3991,10 @@
         <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D107" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3996,10 +4005,10 @@
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D108" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -4010,10 +4019,10 @@
         <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D109" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -4024,10 +4033,10 @@
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D110" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4038,10 +4047,10 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D111" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4052,10 +4061,10 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D112" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4063,10 +4072,10 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D113" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4074,10 +4083,10 @@
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D114" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4085,10 +4094,10 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D115" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4096,10 +4105,10 @@
         <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D116" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4110,10 +4119,10 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D117" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4124,10 +4133,10 @@
         <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D118" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4135,10 +4144,10 @@
         <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D119" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4146,10 +4155,10 @@
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D120" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4157,10 +4166,10 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D121" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4168,10 +4177,10 @@
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D122" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4179,10 +4188,10 @@
         <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D123" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4190,10 +4199,10 @@
         <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D124" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4204,10 +4213,10 @@
         <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D125" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4218,10 +4227,10 @@
         <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D126" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4232,10 +4241,10 @@
         <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D127" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4246,10 +4255,10 @@
         <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D128" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4260,10 +4269,10 @@
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D129" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4274,10 +4283,10 @@
         <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D130" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4288,10 +4297,10 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D131" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4302,10 +4311,10 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D132" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4316,10 +4325,10 @@
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D133" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4330,10 +4339,10 @@
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D134" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4344,10 +4353,10 @@
         <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D135" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4358,10 +4367,10 @@
         <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D136" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4372,10 +4381,10 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D137" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4386,10 +4395,10 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D138" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4400,10 +4409,10 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D139" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4414,10 +4423,10 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4428,10 +4437,10 @@
         <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D141" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4442,10 +4451,10 @@
         <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D142" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4456,10 +4465,10 @@
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D143" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4470,10 +4479,10 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D144" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4484,10 +4493,10 @@
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D145" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4498,10 +4507,10 @@
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D146" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4512,10 +4521,10 @@
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D147" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4526,10 +4535,10 @@
         <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D148" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4540,10 +4549,10 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D149" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4554,10 +4563,10 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D150" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4568,10 +4577,10 @@
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D151" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4582,10 +4591,10 @@
         <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D152" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4596,10 +4605,10 @@
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D153" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4610,10 +4619,10 @@
         <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D154" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4624,10 +4633,10 @@
         <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D155" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4638,10 +4647,10 @@
         <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D156" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4652,10 +4661,10 @@
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D157" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4666,10 +4675,10 @@
         <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D158" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4680,10 +4689,10 @@
         <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D159" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4694,10 +4703,10 @@
         <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D160" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4708,10 +4717,10 @@
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D161" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4722,10 +4731,10 @@
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D162" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4736,10 +4745,10 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D163" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4750,10 +4759,10 @@
         <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D164" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4764,10 +4773,10 @@
         <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D165" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4778,10 +4787,10 @@
         <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D166" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4792,10 +4801,10 @@
         <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D167" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4806,10 +4815,10 @@
         <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D168" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4820,10 +4829,10 @@
         <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D169" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4834,10 +4843,10 @@
         <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D170" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4848,10 +4857,10 @@
         <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D171" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4862,10 +4871,10 @@
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D172" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4876,10 +4885,10 @@
         <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D173" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4890,10 +4899,10 @@
         <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D174" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4904,10 +4913,10 @@
         <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D175" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4918,10 +4927,10 @@
         <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D176" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4932,10 +4941,10 @@
         <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D177" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4946,10 +4955,10 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D178" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4960,10 +4969,10 @@
         <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D179" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4974,10 +4983,10 @@
         <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D180" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4988,10 +4997,10 @@
         <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D181" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -5002,10 +5011,10 @@
         <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D182" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5016,10 +5025,10 @@
         <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D183" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5030,10 +5039,10 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D184" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5044,10 +5053,10 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D185" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5058,10 +5067,10 @@
         <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D186" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5072,10 +5081,10 @@
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D187" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5086,10 +5095,10 @@
         <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D188" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5100,10 +5109,10 @@
         <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D189" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5114,10 +5123,10 @@
         <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D190" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5128,10 +5137,10 @@
         <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D191" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5142,10 +5151,10 @@
         <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D192" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5156,10 +5165,10 @@
         <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D193" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5170,10 +5179,10 @@
         <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D194" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5184,10 +5193,10 @@
         <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D195" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5198,10 +5207,10 @@
         <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D196" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5212,10 +5221,10 @@
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D197" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5226,10 +5235,10 @@
         <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D198" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5240,10 +5249,10 @@
         <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D199" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5254,10 +5263,10 @@
         <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D200" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5268,10 +5277,10 @@
         <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D201" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5282,10 +5291,10 @@
         <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D202" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5296,10 +5305,10 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D203" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5310,10 +5319,10 @@
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D204" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5324,10 +5333,10 @@
         <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D205" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5338,10 +5347,10 @@
         <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D206" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5352,10 +5361,10 @@
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D207" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5366,10 +5375,10 @@
         <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D208" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5380,10 +5389,10 @@
         <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D209" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5394,10 +5403,10 @@
         <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D210" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5408,10 +5417,10 @@
         <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D211" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5422,10 +5431,10 @@
         <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D212" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5436,10 +5445,10 @@
         <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D213" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5450,10 +5459,10 @@
         <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D214" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5464,10 +5473,10 @@
         <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D215" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5478,10 +5487,10 @@
         <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D216" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5492,10 +5501,10 @@
         <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D217" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5506,10 +5515,10 @@
         <v>222</v>
       </c>
       <c r="C218" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D218" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5520,10 +5529,10 @@
         <v>223</v>
       </c>
       <c r="C219" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D219" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5534,10 +5543,10 @@
         <v>224</v>
       </c>
       <c r="C220" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D220" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5548,10 +5557,10 @@
         <v>225</v>
       </c>
       <c r="C221" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D221" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5562,10 +5571,10 @@
         <v>226</v>
       </c>
       <c r="C222" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D222" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5576,10 +5585,10 @@
         <v>227</v>
       </c>
       <c r="C223" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D223" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5590,10 +5599,10 @@
         <v>228</v>
       </c>
       <c r="C224" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D224" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5604,10 +5613,10 @@
         <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D225" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5618,10 +5627,10 @@
         <v>230</v>
       </c>
       <c r="C226" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D226" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5632,10 +5641,10 @@
         <v>231</v>
       </c>
       <c r="C227" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D227" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5646,10 +5655,10 @@
         <v>232</v>
       </c>
       <c r="C228" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D228" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5660,10 +5669,10 @@
         <v>233</v>
       </c>
       <c r="C229" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D229" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5674,10 +5683,10 @@
         <v>234</v>
       </c>
       <c r="C230" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D230" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5688,10 +5697,10 @@
         <v>235</v>
       </c>
       <c r="C231" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D231" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5702,10 +5711,10 @@
         <v>236</v>
       </c>
       <c r="C232" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D232" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5716,10 +5725,10 @@
         <v>237</v>
       </c>
       <c r="C233" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D233" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5730,7 +5739,7 @@
         <v>238</v>
       </c>
       <c r="C234" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D234" t="s">
         <v>238</v>
@@ -5744,7 +5753,7 @@
         <v>239</v>
       </c>
       <c r="C235" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D235" t="s">
         <v>239</v>
@@ -5758,10 +5767,10 @@
         <v>240</v>
       </c>
       <c r="C236" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D236" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5772,10 +5781,10 @@
         <v>241</v>
       </c>
       <c r="C237" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D237" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5786,10 +5795,10 @@
         <v>242</v>
       </c>
       <c r="C238" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D238" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5800,10 +5809,24 @@
         <v>243</v>
       </c>
       <c r="C239" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D239" t="s">
-        <v>717</v>
+        <v>719</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" t="s">
+        <v>4</v>
+      </c>
+      <c r="B240" t="s">
+        <v>244</v>
+      </c>
+      <c r="C240" t="s">
+        <v>483</v>
+      </c>
+      <c r="D240" t="s">
+        <v>720</v>
       </c>
     </row>
   </sheetData>

--- a/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
+++ b/TOOLS_DOI_SOAT/RAU_CU/Danh sách Siêu thị.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="724">
   <si>
     <t>THÔNG TIN KHO</t>
   </si>
@@ -751,6 +751,9 @@
     <t>A243</t>
   </si>
   <si>
+    <t>A216</t>
+  </si>
+  <si>
     <t>-4776256360</t>
   </si>
   <si>
@@ -1468,6 +1471,9 @@
     <t>-1003932619661</t>
   </si>
   <si>
+    <t>-1004361944433</t>
+  </si>
+  <si>
     <t>KFM_BDU_DAN - 27 Tân Lập</t>
   </si>
   <si>
@@ -2177,6 +2183,9 @@
   </si>
   <si>
     <t>KFM_HCM_Q08 - A6-7 Block A Diamond Lotus Riverside</t>
+  </si>
+  <si>
+    <t>KFM_HCM_BCH - CA.01 Đường 19 KDC Phong Phú 4</t>
   </si>
 </sst>
 </file>
@@ -2508,7 +2517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D240"/>
+  <dimension ref="A1:D241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2533,10 +2542,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2547,10 +2556,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2561,10 +2570,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D4" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2575,10 +2584,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D5" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2589,10 +2598,10 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D6" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2603,10 +2612,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D7" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2617,10 +2626,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D8" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2631,10 +2640,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D9" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2645,10 +2654,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D10" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2659,10 +2668,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D11" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2673,10 +2682,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D12" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2687,10 +2696,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D13" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2701,10 +2710,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D14" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2715,10 +2724,10 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D15" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2729,10 +2738,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D16" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2743,10 +2752,10 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2757,10 +2766,10 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D18" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2771,10 +2780,10 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D19" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2785,10 +2794,10 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D20" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2799,10 +2808,10 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D21" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2813,10 +2822,10 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D22" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2827,10 +2836,10 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2841,10 +2850,10 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D24" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2855,10 +2864,10 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D25" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2869,10 +2878,10 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D26" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2883,10 +2892,10 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D27" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2897,10 +2906,10 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D28" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2911,10 +2920,10 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D29" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2925,10 +2934,10 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D30" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2939,10 +2948,10 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2953,10 +2962,10 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D32" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2967,10 +2976,10 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D33" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2981,10 +2990,10 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D34" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2995,10 +3004,10 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D35" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3009,10 +3018,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D36" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3023,10 +3032,10 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D37" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3037,10 +3046,10 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D38" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3051,10 +3060,10 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D39" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3065,10 +3074,10 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D40" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3079,10 +3088,10 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D41" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3093,10 +3102,10 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D42" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3107,10 +3116,10 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D43" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3121,10 +3130,10 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D44" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3135,10 +3144,10 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D45" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3149,10 +3158,10 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D46" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3163,10 +3172,10 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D47" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3177,10 +3186,10 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D48" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3191,10 +3200,10 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D49" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3205,10 +3214,10 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D50" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3219,10 +3228,10 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D51" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3233,10 +3242,10 @@
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D52" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3247,10 +3256,10 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D53" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3261,10 +3270,10 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D54" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3275,10 +3284,10 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D55" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3289,10 +3298,10 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D56" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3303,10 +3312,10 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D57" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3317,10 +3326,10 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D58" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3331,10 +3340,10 @@
         <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D59" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3345,10 +3354,10 @@
         <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D60" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3359,10 +3368,10 @@
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D61" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3373,10 +3382,10 @@
         <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D62" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3387,10 +3396,10 @@
         <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D63" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3401,10 +3410,10 @@
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D64" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3415,10 +3424,10 @@
         <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D65" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3429,10 +3438,10 @@
         <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D66" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3443,10 +3452,10 @@
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D67" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3457,10 +3466,10 @@
         <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D68" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3471,10 +3480,10 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D69" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3485,10 +3494,10 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D70" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3499,10 +3508,10 @@
         <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D71" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3513,10 +3522,10 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D72" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3527,10 +3536,10 @@
         <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D73" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3541,10 +3550,10 @@
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D74" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3555,10 +3564,10 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D75" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3569,10 +3578,10 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D76" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3583,10 +3592,10 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D77" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3597,10 +3606,10 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D78" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3611,10 +3620,10 @@
         <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D79" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3625,10 +3634,10 @@
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D80" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3639,10 +3648,10 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D81" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3653,10 +3662,10 @@
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D82" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3667,10 +3676,10 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D83" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3681,10 +3690,10 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D84" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3695,10 +3704,10 @@
         <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D85" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3709,10 +3718,10 @@
         <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D86" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3723,10 +3732,10 @@
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D87" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3737,10 +3746,10 @@
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D88" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3751,10 +3760,10 @@
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D89" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3762,10 +3771,10 @@
         <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D90" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3776,10 +3785,10 @@
         <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D91" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3790,10 +3799,10 @@
         <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D92" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3804,10 +3813,10 @@
         <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D93" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3818,10 +3827,10 @@
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D94" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3832,10 +3841,10 @@
         <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D95" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3846,10 +3855,10 @@
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D96" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3860,10 +3869,10 @@
         <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D97" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3874,10 +3883,10 @@
         <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D98" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3888,10 +3897,10 @@
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D99" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3899,10 +3908,10 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D100" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3913,10 +3922,10 @@
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D101" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3927,10 +3936,10 @@
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D102" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3941,10 +3950,10 @@
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D103" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3955,10 +3964,10 @@
         <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D104" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3966,10 +3975,10 @@
         <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D105" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3980,10 +3989,10 @@
         <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D106" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3991,10 +4000,10 @@
         <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D107" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -4005,10 +4014,10 @@
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D108" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -4019,10 +4028,10 @@
         <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D109" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -4033,10 +4042,10 @@
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D110" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4047,10 +4056,10 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D111" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4061,10 +4070,10 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D112" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4072,10 +4081,10 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D113" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4083,10 +4092,10 @@
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D114" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4094,10 +4103,10 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D115" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4105,10 +4114,10 @@
         <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D116" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4119,10 +4128,10 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D117" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4133,10 +4142,10 @@
         <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D118" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4144,10 +4153,10 @@
         <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D119" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4155,10 +4164,10 @@
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D120" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4166,10 +4175,10 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D121" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4177,10 +4186,10 @@
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D122" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4188,10 +4197,10 @@
         <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D123" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4199,10 +4208,10 @@
         <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D124" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4213,10 +4222,10 @@
         <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D125" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4227,10 +4236,10 @@
         <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D126" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4241,10 +4250,10 @@
         <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D127" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4255,10 +4264,10 @@
         <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D128" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4269,10 +4278,10 @@
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D129" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4283,10 +4292,10 @@
         <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D130" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4297,10 +4306,10 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D131" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4311,10 +4320,10 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D132" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4325,10 +4334,10 @@
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D133" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4339,10 +4348,10 @@
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D134" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4353,10 +4362,10 @@
         <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D135" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4367,10 +4376,10 @@
         <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D136" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4381,10 +4390,10 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D137" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4395,10 +4404,10 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D138" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4409,10 +4418,10 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D139" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4423,10 +4432,10 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4437,10 +4446,10 @@
         <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D141" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4451,10 +4460,10 @@
         <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D142" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4465,10 +4474,10 @@
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D143" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4479,10 +4488,10 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D144" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4493,10 +4502,10 @@
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D145" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4507,10 +4516,10 @@
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D146" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4521,10 +4530,10 @@
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D147" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4535,10 +4544,10 @@
         <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D148" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4549,10 +4558,10 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D149" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4563,10 +4572,10 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D150" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4577,10 +4586,10 @@
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D151" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4591,10 +4600,10 @@
         <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D152" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4605,10 +4614,10 @@
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D153" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4619,10 +4628,10 @@
         <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D154" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4633,10 +4642,10 @@
         <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D155" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4647,10 +4656,10 @@
         <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D156" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4661,10 +4670,10 @@
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D157" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4675,10 +4684,10 @@
         <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D158" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4689,10 +4698,10 @@
         <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D159" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4703,10 +4712,10 @@
         <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D160" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4717,10 +4726,10 @@
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D161" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4731,10 +4740,10 @@
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D162" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4745,10 +4754,10 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D163" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4759,10 +4768,10 @@
         <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D164" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4773,10 +4782,10 @@
         <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D165" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4787,10 +4796,10 @@
         <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D166" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4801,10 +4810,10 @@
         <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D167" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4815,10 +4824,10 @@
         <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D168" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4829,10 +4838,10 @@
         <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D169" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4843,10 +4852,10 @@
         <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D170" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4857,10 +4866,10 @@
         <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D171" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4871,10 +4880,10 @@
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D172" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4885,10 +4894,10 @@
         <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D173" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4899,10 +4908,10 @@
         <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D174" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4913,10 +4922,10 @@
         <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D175" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4927,10 +4936,10 @@
         <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D176" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4941,10 +4950,10 @@
         <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D177" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4955,10 +4964,10 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D178" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4969,10 +4978,10 @@
         <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D179" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4983,10 +4992,10 @@
         <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D180" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4997,10 +5006,10 @@
         <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D181" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -5011,10 +5020,10 @@
         <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D182" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5025,10 +5034,10 @@
         <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D183" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5039,10 +5048,10 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D184" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5053,10 +5062,10 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D185" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5067,10 +5076,10 @@
         <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D186" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5081,10 +5090,10 @@
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D187" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5095,10 +5104,10 @@
         <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D188" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5109,10 +5118,10 @@
         <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D189" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5123,10 +5132,10 @@
         <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D190" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5137,10 +5146,10 @@
         <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D191" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5151,10 +5160,10 @@
         <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D192" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5165,10 +5174,10 @@
         <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D193" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5179,10 +5188,10 @@
         <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D194" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5193,10 +5202,10 @@
         <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D195" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5207,10 +5216,10 @@
         <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D196" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5221,10 +5230,10 @@
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D197" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5235,10 +5244,10 @@
         <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D198" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5249,10 +5258,10 @@
         <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D199" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5263,10 +5272,10 @@
         <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D200" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5277,10 +5286,10 @@
         <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D201" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5291,10 +5300,10 @@
         <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D202" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5305,10 +5314,10 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D203" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5319,10 +5328,10 @@
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D204" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5333,10 +5342,10 @@
         <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D205" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5347,10 +5356,10 @@
         <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D206" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5361,10 +5370,10 @@
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D207" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5375,10 +5384,10 @@
         <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D208" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5389,10 +5398,10 @@
         <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D209" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5403,10 +5412,10 @@
         <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D210" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5417,10 +5426,10 @@
         <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D211" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5431,10 +5440,10 @@
         <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D212" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5445,10 +5454,10 @@
         <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D213" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5459,10 +5468,10 @@
         <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D214" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5473,10 +5482,10 @@
         <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D215" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5487,10 +5496,10 @@
         <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D216" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5501,10 +5510,10 @@
         <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D217" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5515,10 +5524,10 @@
         <v>222</v>
       </c>
       <c r="C218" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D218" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5529,10 +5538,10 @@
         <v>223</v>
       </c>
       <c r="C219" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D219" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5543,10 +5552,10 @@
         <v>224</v>
       </c>
       <c r="C220" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D220" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5557,10 +5566,10 @@
         <v>225</v>
       </c>
       <c r="C221" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D221" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5571,10 +5580,10 @@
         <v>226</v>
       </c>
       <c r="C222" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D222" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5585,10 +5594,10 @@
         <v>227</v>
       </c>
       <c r="C223" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D223" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5599,10 +5608,10 @@
         <v>228</v>
       </c>
       <c r="C224" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D224" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5613,10 +5622,10 @@
         <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D225" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5627,10 +5636,10 @@
         <v>230</v>
       </c>
       <c r="C226" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D226" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5641,10 +5650,10 @@
         <v>231</v>
       </c>
       <c r="C227" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D227" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5655,10 +5664,10 @@
         <v>232</v>
       </c>
       <c r="C228" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D228" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5669,10 +5678,10 @@
         <v>233</v>
       </c>
       <c r="C229" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D229" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5683,10 +5692,10 @@
         <v>234</v>
       </c>
       <c r="C230" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D230" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5697,10 +5706,10 @@
         <v>235</v>
       </c>
       <c r="C231" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D231" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5711,10 +5720,10 @@
         <v>236</v>
       </c>
       <c r="C232" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D232" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5725,10 +5734,10 @@
         <v>237</v>
       </c>
       <c r="C233" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D233" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5739,7 +5748,7 @@
         <v>238</v>
       </c>
       <c r="C234" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D234" t="s">
         <v>238</v>
@@ -5753,7 +5762,7 @@
         <v>239</v>
       </c>
       <c r="C235" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D235" t="s">
         <v>239</v>
@@ -5767,10 +5776,10 @@
         <v>240</v>
       </c>
       <c r="C236" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D236" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5781,10 +5790,10 @@
         <v>241</v>
       </c>
       <c r="C237" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D237" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5795,10 +5804,10 @@
         <v>242</v>
       </c>
       <c r="C238" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D238" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5809,10 +5818,10 @@
         <v>243</v>
       </c>
       <c r="C239" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D239" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5823,10 +5832,24 @@
         <v>244</v>
       </c>
       <c r="C240" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D240" t="s">
-        <v>720</v>
+        <v>722</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" t="s">
+        <v>4</v>
+      </c>
+      <c r="B241" t="s">
+        <v>245</v>
+      </c>
+      <c r="C241" t="s">
+        <v>485</v>
+      </c>
+      <c r="D241" t="s">
+        <v>723</v>
       </c>
     </row>
   </sheetData>
